--- a/其它格式未转换/耶稣家谱/耶稣家谱.xlsx
+++ b/其它格式未转换/耶稣家谱/耶稣家谱.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文件\notes\历史\宗教史\耶稣家谱\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文件\notes\其它格式未转换\耶稣家谱\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A458BDC3-B9D1-4D88-A8B3-56DFC50C7267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71BEC3A-574A-4AC6-AF0F-99FB594F3B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="圣经原文" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="121">
   <si>
     <t>神</t>
   </si>
@@ -418,6 +418,23 @@
   </si>
   <si>
     <t xml:space="preserve">14 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚法撒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《旧约》（创10:24）（历上1:18）引用的是希伯来原文，没有该南。
+《新约》（路加3:36）引用的是希腊文《七十士译本》，包含该南。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创世纪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -473,7 +490,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -510,8 +527,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -532,15 +555,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -602,7 +616,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -639,22 +653,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -666,61 +677,73 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -999,1240 +1022,1565 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3898ED4-D009-40BA-95B4-9482A98C85DE}">
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.4140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="14.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.08203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="30.08203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.4140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28" style="1" customWidth="1"/>
+    <col min="7" max="8" width="14.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="42.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:9" ht="42.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="30" t="s">
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="41"/>
+      <c r="B2" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="I2" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="2">
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="H3" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I3" s="35"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="B4" s="24" t="s">
+        <v>1</v>
+      </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="2">
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2">
         <v>0</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="H4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I4" s="2"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="B5" s="24" t="s">
+        <v>97</v>
+      </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="2">
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="H5" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I5" s="2"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2">
+      <c r="B6" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="C6" s="24"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2">
         <v>2</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H6" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="B7" s="24" t="s">
+        <v>3</v>
+      </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="2">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2">
         <v>3</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="H7" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="B8" s="24" t="s">
+        <v>4</v>
+      </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="2">
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2">
         <v>4</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="H8" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I8" s="2"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="B9" s="24" t="s">
+        <v>5</v>
+      </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="2">
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2">
         <v>5</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="H9" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="B10" s="24" t="s">
+        <v>6</v>
+      </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="2">
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
         <v>6</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="H10" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="B11" s="24" t="s">
+        <v>98</v>
+      </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="2">
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2">
         <v>7</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="H11" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="B12" s="24" t="s">
+        <v>7</v>
+      </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="2">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2">
         <v>8</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="H12" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="B13" s="24" t="s">
+        <v>8</v>
+      </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="2">
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2">
         <v>9</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="H13" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="B14" s="24" t="s">
+        <v>9</v>
+      </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="2">
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2">
         <v>10</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="H14" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="B15" s="18" t="s">
+        <v>117</v>
+      </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2">
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2">
         <v>11</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="H15" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="I15" s="2"/>
+    </row>
+    <row r="16" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2">
+        <v>12</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2">
+        <v>13</v>
+      </c>
+      <c r="H17" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2">
+        <v>14</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="2"/>
+      <c r="B19" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2">
+        <v>15</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2">
+        <v>16</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2">
+        <v>17</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2">
+        <v>18</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2">
+        <v>19</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="2"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="11">
+        <v>1</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="2">
+        <v>20</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="11">
+        <v>2</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2">
+        <v>21</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="11">
+        <v>3</v>
+      </c>
+      <c r="E26" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2">
+        <v>22</v>
+      </c>
+      <c r="H26" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="11">
+        <v>4</v>
+      </c>
+      <c r="E27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2">
+        <v>23</v>
+      </c>
+      <c r="H27" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="11">
+        <v>5</v>
+      </c>
+      <c r="E28" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2">
+        <v>24</v>
+      </c>
+      <c r="H28" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="11">
+        <v>6</v>
+      </c>
+      <c r="E29" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2">
+        <v>25</v>
+      </c>
+      <c r="H29" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="11">
+        <v>7</v>
+      </c>
+      <c r="E30" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2">
+        <v>26</v>
+      </c>
+      <c r="H30" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="11">
+        <v>8</v>
+      </c>
+      <c r="E31" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2">
+        <v>27</v>
+      </c>
+      <c r="H31" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="2"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="11">
+        <v>9</v>
+      </c>
+      <c r="E32" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2">
+        <v>28</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="11">
         <v>10</v>
       </c>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" ht="98" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2">
+      <c r="E33" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2">
+        <v>29</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="I33" s="2"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="11">
+        <v>11</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2">
+        <v>30</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="2"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="11">
         <v>12</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E35" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2">
+        <v>31</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="I35" s="2"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="11">
+        <v>13</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2">
+        <v>32</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="I36" s="2"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4">
+        <v>33</v>
+      </c>
+      <c r="H37" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="11">
+        <v>2</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="2">
+        <v>34</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="3"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="11">
         <v>3</v>
       </c>
-      <c r="F16" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2">
+      <c r="E39" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2">
+        <v>35</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="I39" s="2"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="11">
+        <v>4</v>
+      </c>
+      <c r="E40" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2">
+        <v>36</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="11">
+        <v>5</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2">
+        <v>37</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="11">
+        <v>6</v>
+      </c>
+      <c r="E42" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2">
+        <v>38</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="11">
+        <v>7</v>
+      </c>
+      <c r="E43" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="G43" s="2">
+        <v>39</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9" ht="98" x14ac:dyDescent="0.3">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="11">
+        <v>8</v>
+      </c>
+      <c r="E44" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="G44" s="2">
+        <v>40</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="11">
+        <v>9</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2">
+        <v>41</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="11">
+        <v>10</v>
+      </c>
+      <c r="E46" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2">
+        <v>42</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="11">
+        <v>11</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2">
+        <v>43</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="11">
+        <v>12</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2">
+        <v>44</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="11">
         <v>13</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E49" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2">
+        <v>45</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2">
+        <v>46</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:9" ht="70" x14ac:dyDescent="0.3">
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="11">
+        <v>1</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G51" s="2">
+        <v>47</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="11">
+        <v>2</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F52" s="6"/>
+      <c r="G52" s="2">
+        <v>48</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:9" ht="42" x14ac:dyDescent="0.3">
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="11">
+        <v>3</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="G53" s="2">
+        <v>49</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:9" ht="28" x14ac:dyDescent="0.3">
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="11">
+        <v>4</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="G54" s="2">
+        <v>50</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="11">
+        <v>5</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G55" s="2">
+        <v>51</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="11">
+        <v>6</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G56" s="2">
+        <v>52</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="11">
+        <v>7</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G57" s="2">
+        <v>53</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="11">
+        <v>8</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G58" s="2">
+        <v>54</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="11">
+        <v>9</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G59" s="2">
+        <v>55</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I59" s="2"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="2"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="11">
+        <v>10</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G60" s="2">
+        <v>56</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="11">
         <v>11</v>
       </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2">
-        <v>14</v>
-      </c>
-      <c r="E18" s="25" t="s">
+      <c r="E61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G61" s="2">
+        <v>57</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="2"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="11">
         <v>12</v>
       </c>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2">
-        <v>15</v>
-      </c>
-      <c r="E19" s="25" t="s">
+      <c r="E62" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G62" s="2">
+        <v>58</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I62" s="2"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="2"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="11">
         <v>13</v>
-      </c>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2">
-        <v>16</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2">
-        <v>17</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2">
-        <v>18</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2">
-        <v>19</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="11">
-        <v>1</v>
-      </c>
-      <c r="B24" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="3"/>
-      <c r="D24" s="2">
-        <v>20</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="11">
-        <v>2</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2">
-        <v>21</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="11">
-        <v>3</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2">
-        <v>22</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="11">
-        <v>4</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2">
-        <v>23</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="11">
-        <v>5</v>
-      </c>
-      <c r="B28" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2">
-        <v>24</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="11">
-        <v>6</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2">
-        <v>25</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="11">
-        <v>7</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2">
-        <v>26</v>
-      </c>
-      <c r="E30" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="11">
-        <v>8</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2">
-        <v>27</v>
-      </c>
-      <c r="E31" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="11">
-        <v>9</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2">
-        <v>28</v>
-      </c>
-      <c r="E32" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="11">
-        <v>10</v>
-      </c>
-      <c r="B33" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2">
-        <v>29</v>
-      </c>
-      <c r="E33" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="11">
-        <v>11</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2">
-        <v>30</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="11">
-        <v>12</v>
-      </c>
-      <c r="B35" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2">
-        <v>31</v>
-      </c>
-      <c r="E35" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="11">
-        <v>13</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2">
-        <v>32</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4">
-        <v>33</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="4"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="11">
-        <v>2</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="3"/>
-      <c r="D38" s="2">
-        <v>34</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="3"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="11">
-        <v>3</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2">
-        <v>35</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="11">
-        <v>4</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2">
-        <v>36</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="11">
-        <v>5</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2">
-        <v>37</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="11">
-        <v>6</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2">
-        <v>38</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="11">
-        <v>7</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="6"/>
-      <c r="D43" s="2">
-        <v>39</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="1:6" ht="98" x14ac:dyDescent="0.3">
-      <c r="A44" s="11">
-        <v>8</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C44" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="2">
-        <v>40</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="11">
-        <v>9</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2">
-        <v>41</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="11">
-        <v>10</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2">
-        <v>42</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="11">
-        <v>11</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2">
-        <v>43</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="11">
-        <v>12</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2">
-        <v>44</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F48" s="2"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="11">
-        <v>13</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2">
-        <v>45</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F49" s="2"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2">
-        <v>46</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F50" s="2"/>
-    </row>
-    <row r="51" spans="1:6" ht="70" x14ac:dyDescent="0.3">
-      <c r="A51" s="11">
-        <v>1</v>
-      </c>
-      <c r="B51" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C51" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="2">
-        <v>47</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F51" s="2"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="11">
-        <v>2</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C52" s="6"/>
-      <c r="D52" s="2">
-        <v>48</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F52" s="2"/>
-    </row>
-    <row r="53" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A53" s="11">
-        <v>3</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="24" t="s">
-        <v>110</v>
-      </c>
-      <c r="D53" s="2">
-        <v>49</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F53" s="2"/>
-    </row>
-    <row r="54" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A54" s="11">
-        <v>4</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="D54" s="2">
-        <v>50</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F54" s="2"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="11">
-        <v>5</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D55" s="2">
-        <v>51</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F55" s="2"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="11">
-        <v>6</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D56" s="2">
-        <v>52</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F56" s="2"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="11">
-        <v>7</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D57" s="2">
-        <v>53</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="11">
-        <v>8</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D58" s="2">
-        <v>54</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="11">
-        <v>9</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D59" s="2">
-        <v>55</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F59" s="2"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="11">
-        <v>10</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" s="2">
-        <v>56</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F60" s="2"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="11">
-        <v>11</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D61" s="2">
-        <v>57</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F61" s="2"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="11">
-        <v>12</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D62" s="2">
-        <v>58</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="11">
-        <v>13</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D63" s="2">
-        <v>59</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F63" s="2"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="10" t="s">
+      <c r="F63" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="G63" s="2">
+        <v>59</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I63" s="2"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="2"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2">
+      <c r="F64" s="2"/>
+      <c r="G64" s="2">
         <v>60</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="H64" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F64" s="2"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I64" s="2"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-      <c r="D65" s="2">
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2">
         <v>61</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="H65" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F65" s="2"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I65" s="2"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
-      <c r="D66" s="2">
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2">
         <v>62</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="H66" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F66" s="2"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I66" s="2"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
-      <c r="D67" s="2">
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2">
         <v>63</v>
       </c>
-      <c r="E67" s="2" t="s">
+      <c r="H67" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F67" s="2"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I67" s="2"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
-      <c r="D68" s="2">
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2">
         <v>64</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="H68" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F68" s="2"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I68" s="2"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
-      <c r="D69" s="2">
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2">
         <v>65</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="H69" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F69" s="2"/>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I69" s="2"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
-      <c r="D70" s="2">
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2">
         <v>66</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="H70" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F70" s="2"/>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I70" s="2"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-      <c r="D71" s="2">
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2">
         <v>67</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="H71" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F71" s="2"/>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I71" s="2"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
-      <c r="D72" s="2">
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2">
         <v>68</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="H72" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F72" s="2"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I72" s="2"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
-      <c r="D73" s="2">
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2">
         <v>69</v>
       </c>
-      <c r="E73" s="2" t="s">
+      <c r="H73" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F73" s="2"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I73" s="2"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
-      <c r="D74" s="2">
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2">
         <v>70</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="H74" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F74" s="2"/>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I74" s="2"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
-      <c r="D75" s="2">
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2">
         <v>71</v>
       </c>
-      <c r="E75" s="2" t="s">
+      <c r="H75" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F75" s="2"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I75" s="2"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-      <c r="D76" s="2">
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="2">
         <v>72</v>
       </c>
-      <c r="E76" s="6" t="s">
+      <c r="H76" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I76" s="6"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
-      <c r="D77" s="2">
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2">
         <v>73</v>
       </c>
-      <c r="E77" s="6" t="s">
+      <c r="H77" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F77" s="6"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I77" s="6"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
-      <c r="D78" s="2">
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2">
         <v>74</v>
       </c>
-      <c r="E78" s="2" t="s">
+      <c r="H78" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F78" s="2"/>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
-      <c r="D79" s="2">
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2">
         <v>75</v>
       </c>
-      <c r="E79" s="2" t="s">
+      <c r="H79" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F79" s="2"/>
+      <c r="I79" s="2"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="G1:I1"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C54" r:id="rId1" location="%E6%89%80%E7%BD%97%E5%B7%B4%E4%BC%AF%E7%9A%84%E5%84%BF%E5%AD%90" display="耶稣的谱系#所罗巴伯的儿子" xr:uid="{54F552CE-A939-493B-8918-9063DDDF512C}"/>
-    <hyperlink ref="B43" r:id="rId2" tooltip="约兰 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E8%98%AD_(%E7%8C%B6%E5%A4%A7)" xr:uid="{52C2BA8B-5ECE-42B9-9E6C-A04B094B3B9E}"/>
-    <hyperlink ref="B42" r:id="rId3" tooltip="约沙法" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E6%B2%99%E6%B3%95" xr:uid="{B59F982E-DD72-467C-8B00-AAA40331BBC9}"/>
-    <hyperlink ref="B41" r:id="rId4" tooltip="亚撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E6%92%92" xr:uid="{A676C111-98F8-4E28-8611-1BDF1FC30B26}"/>
-    <hyperlink ref="B40" r:id="rId5" tooltip="亚比央" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E6%AF%94%E5%A4%AE" xr:uid="{57C451CF-E122-4EC6-9EFD-528D899E3F29}"/>
-    <hyperlink ref="B39" r:id="rId6" tooltip="罗波安" display="https://zh.wikipedia.org/wiki/%E7%BE%85%E6%B3%A2%E5%AE%89" xr:uid="{4D227C43-BBFE-41B2-8B88-F2708BB888E3}"/>
-    <hyperlink ref="B38" r:id="rId7" tooltip="所罗门 (君王)" display="https://zh.wikipedia.org/wiki/%E6%89%80%E7%BE%85%E9%96%80_(%E5%90%9B%E7%8E%8B)" xr:uid="{F89BBBD8-3B29-4041-9F50-C47E1FC9DDED}"/>
-    <hyperlink ref="B37" r:id="rId8" tooltip="大卫王" display="https://zh.wikipedia.org/wiki/%E5%A4%A7%E8%A1%9B%E7%8E%8B" xr:uid="{56A7D6C7-26AA-47DA-85B6-7F89B92C4DD8}"/>
-    <hyperlink ref="B24" r:id="rId9" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{AB26EAD3-2D25-446C-B7DF-D9AC554B887C}"/>
-    <hyperlink ref="B25" r:id="rId10" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{F2B42AF0-FDFD-4B2C-9F9F-8C45A36138F3}"/>
-    <hyperlink ref="B26" r:id="rId11" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{77651F01-29D9-4DCB-848D-E80E8C560788}"/>
-    <hyperlink ref="B27" r:id="rId12" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{E90359D2-4200-458A-BC2A-55AEBB996A43}"/>
-    <hyperlink ref="B28" r:id="rId13" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{4E5C2745-ACD5-4C74-A5F5-4FD837AFAE30}"/>
-    <hyperlink ref="B29" r:id="rId14" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{5A9A3FA2-4296-48EE-8C43-C291D44CA4A2}"/>
-    <hyperlink ref="B30" r:id="rId15" tooltip="亚兰" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E5%85%B0" xr:uid="{83896BBE-33B4-430A-A9D6-027F40A5EF56}"/>
-    <hyperlink ref="B31" r:id="rId16" tooltip="亚米拿达" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E7%B1%B3%E6%8B%BF%E8%BE%BE" xr:uid="{AD76F7C8-8520-4820-8E59-5F7949882E07}"/>
-    <hyperlink ref="B32" r:id="rId17" tooltip="拿顺" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%A1%BA" xr:uid="{3D372BF3-E2B4-48C4-994F-3EA8F87944C7}"/>
-    <hyperlink ref="B33" r:id="rId18" tooltip="撒门" display="https://zh.wikipedia.org/wiki/%E6%92%92%E9%97%A8" xr:uid="{E5213FF4-5133-432C-B833-690A5DCFBDAC}"/>
-    <hyperlink ref="B34" r:id="rId19" tooltip="波阿斯" display="https://zh.wikipedia.org/wiki/%E6%B3%A2%E9%98%BF%E6%96%AF" xr:uid="{B10BBF17-640C-4F13-BF71-029201BF677D}"/>
-    <hyperlink ref="B35" r:id="rId20" tooltip="俄备得" display="https://zh.wikipedia.org/wiki/%E4%BF%84%E5%A4%87%E5%BE%97" xr:uid="{511B802D-143F-4476-BE02-789D35011D3B}"/>
-    <hyperlink ref="B36" r:id="rId21" tooltip="耶西" display="https://zh.wikipedia.org/wiki/%E8%80%B6%E8%A5%BF" xr:uid="{640F03ED-E19C-444F-B433-04003D895D45}"/>
-    <hyperlink ref="E37" r:id="rId22" tooltip="大卫王" display="https://zh.wikipedia.org/wiki/%E5%A4%A7%E8%A1%9B%E7%8E%8B" xr:uid="{AC65AEF8-5BC2-432B-99E3-1B237ECEDF85}"/>
-    <hyperlink ref="E4" r:id="rId23" tooltip="亚当" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E7%95%B6" xr:uid="{FF35CB0F-ADF7-4440-A7E4-012E5A5926CF}"/>
-    <hyperlink ref="E5" r:id="rId24" tooltip="塞特" display="https://zh.wikipedia.org/wiki/%E5%A1%9E%E7%89%B9" xr:uid="{9169DB06-65EB-4C01-AB8F-9EEEA0793CAB}"/>
-    <hyperlink ref="E6" r:id="rId25" tooltip="以挪士" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%8C%AA%E5%A3%AB" xr:uid="{1ADEE73F-6EE5-4F42-8A99-309C0390CF17}"/>
-    <hyperlink ref="E7" r:id="rId26" tooltip="该南" display="https://zh.wikipedia.org/wiki/%E8%AF%A5%E5%8D%97" xr:uid="{4B3359C4-3F44-4215-8F0A-7214B391D814}"/>
-    <hyperlink ref="E8" r:id="rId27" tooltip="玛勒列" display="https://zh.wikipedia.org/wiki/%E7%8E%9B%E5%8B%92%E5%88%97" xr:uid="{95351270-C25C-49CF-A2AC-8B7154C90EED}"/>
-    <hyperlink ref="E9" r:id="rId28" tooltip="雅列" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%88%97" xr:uid="{ACEC4366-E2A2-49D9-A83C-49F1C0CE6540}"/>
-    <hyperlink ref="E10" r:id="rId29" tooltip="以诺" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E8%AB%BE" xr:uid="{3447F6F4-A1AB-4F5E-A201-6BE4B222437A}"/>
-    <hyperlink ref="E11" r:id="rId30" tooltip="玛土撒拉" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E5%9C%9F%E6%92%92%E6%8B%89" xr:uid="{45D2DB60-9AED-45B2-AD66-B5B37EC8E712}"/>
-    <hyperlink ref="E12" r:id="rId31" tooltip="拉麦" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E9%BA%A6" xr:uid="{41E2BE11-4D08-431B-9BD6-3236655F5255}"/>
-    <hyperlink ref="E13" r:id="rId32" tooltip="挪亚" display="https://zh.wikipedia.org/wiki/%E6%8C%AA%E4%BA%9E" xr:uid="{79F73FE6-51FD-4324-9AAD-16135AB1DD8B}"/>
-    <hyperlink ref="E14" r:id="rId33" tooltip="闪 (圣经)" display="https://zh.wikipedia.org/wiki/%E9%96%83_(%E8%81%96%E7%B6%93)" xr:uid="{84177492-4E71-4A6E-82EB-9099408F9F54}"/>
-    <hyperlink ref="E15" r:id="rId34" tooltip="亚法撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E6%B3%95%E6%92%92" xr:uid="{233F9479-DCA3-4915-8187-63F1001850F5}"/>
-    <hyperlink ref="E17" r:id="rId35" tooltip="沙拉 (圣经人物)" display="https://zh.wikipedia.org/wiki/%E6%B2%99%E6%8B%89_(%E5%9C%A3%E7%BB%8F%E4%BA%BA%E7%89%A9)" xr:uid="{0E57A2B1-02AC-4283-BEE9-29E6311064C4}"/>
-    <hyperlink ref="E18" r:id="rId36" tooltip="希伯" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E4%BC%AF" xr:uid="{534809CC-247C-46D1-B2E4-CED8F44B17DA}"/>
-    <hyperlink ref="E19" r:id="rId37" tooltip="法勒" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92" xr:uid="{6DE726CE-F659-499C-AAFC-6343784BADFE}"/>
-    <hyperlink ref="E20" r:id="rId38" tooltip="拉吴" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E5%90%B4" xr:uid="{E682953A-CD35-4E2F-942C-B4ED6682DDAE}"/>
-    <hyperlink ref="E21" r:id="rId39" tooltip="西鹿" display="https://zh.wikipedia.org/wiki/%E8%A5%BF%E9%B9%BF" xr:uid="{D42A9EA5-BA38-4053-B37D-EE22C85DB73D}"/>
-    <hyperlink ref="E22" r:id="rId40" tooltip="拿鹤" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%B9%A4" xr:uid="{CA8B6393-8FED-4235-B3A5-21B9255D0DE1}"/>
-    <hyperlink ref="E23" r:id="rId41" tooltip="他拉" display="https://zh.wikipedia.org/wiki/%E4%BB%96%E6%8B%89" xr:uid="{C2994B2D-1F9B-492E-8F29-BC298694C868}"/>
-    <hyperlink ref="E24" r:id="rId42" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{63D8363D-B530-4CF6-91F3-BD042ECCAC8D}"/>
-    <hyperlink ref="E25" r:id="rId43" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{70B7F414-BB95-4A8C-9A3D-6E291A34A1F9}"/>
-    <hyperlink ref="E26" r:id="rId44" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{2860D780-F11A-4C03-AD36-27B400A33726}"/>
-    <hyperlink ref="E27" r:id="rId45" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{6CBA7CED-39C8-48D6-8C75-76669537007A}"/>
-    <hyperlink ref="E28" r:id="rId46" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{E83B196D-0180-497D-AE5C-B7F21D9146DF}"/>
-    <hyperlink ref="E29" r:id="rId47" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{0E3BB2A0-C600-4754-B61E-66995A4F2BF5}"/>
-    <hyperlink ref="E30" r:id="rId48" tooltip="亚兰" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E5%85%B0" xr:uid="{7DB98F20-15A9-44C4-A04C-446DCBF285FF}"/>
-    <hyperlink ref="E31" r:id="rId49" tooltip="亚米拿达" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E7%B1%B3%E6%8B%BF%E8%BE%BE" xr:uid="{7AA27047-62D6-4044-9E49-2D7AD0967610}"/>
-    <hyperlink ref="E32" r:id="rId50" tooltip="拿顺" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%A1%BA" xr:uid="{1FB7A8C9-6415-4379-90F0-F65A5F10588F}"/>
-    <hyperlink ref="E33" r:id="rId51" tooltip="撒门" display="https://zh.wikipedia.org/wiki/%E6%92%92%E9%97%A8" xr:uid="{C9542CC7-3E57-4474-9867-5356C40CAC08}"/>
-    <hyperlink ref="E34" r:id="rId52" tooltip="波阿斯" display="https://zh.wikipedia.org/wiki/%E6%B3%A2%E9%98%BF%E6%96%AF" xr:uid="{5C9F88C7-B2BE-4A57-8A14-D37A10C149B7}"/>
-    <hyperlink ref="E35" r:id="rId53" tooltip="俄备得" display="https://zh.wikipedia.org/wiki/%E4%BF%84%E5%A4%87%E5%BE%97" xr:uid="{2ACE66BD-AFA7-4C5A-B203-8D789A3528ED}"/>
-    <hyperlink ref="E36" r:id="rId54" tooltip="耶西" display="https://zh.wikipedia.org/wiki/%E8%80%B6%E8%A5%BF" xr:uid="{779E1BF0-8B9C-47B9-9FFA-DEE550B98674}"/>
-    <hyperlink ref="B50" r:id="rId55" tooltip="约西亚" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E8%A5%BF%E4%BA%9E" xr:uid="{4D696DF6-1005-44B3-86F4-90F920A861DC}"/>
-    <hyperlink ref="B49" r:id="rId56" tooltip="亚们" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%80%91" xr:uid="{E70AFC90-3B93-4F15-8176-EB01E1B80657}"/>
-    <hyperlink ref="B48" r:id="rId57" tooltip="玛拿西 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E6%8B%BF%E8%A5%BF_(%E7%8C%B6%E5%A4%A7)" xr:uid="{271247F8-BA63-4867-83BF-BAE0721A7A43}"/>
-    <hyperlink ref="B47" r:id="rId58" tooltip="希西家" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E8%A5%BF%E5%AE%B6" xr:uid="{B3E5C22E-6B7D-4620-B001-CB824FAA924E}"/>
-    <hyperlink ref="B46" r:id="rId59" tooltip="亚哈斯" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%93%88%E6%96%AF" xr:uid="{B153943D-19EF-4D83-965B-568A39FBA15F}"/>
-    <hyperlink ref="B45" r:id="rId60" tooltip="约坦" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E5%9D%A6" xr:uid="{404F7698-EB07-4F78-B8F7-2956FD0DCE1E}"/>
-    <hyperlink ref="B53" r:id="rId61" xr:uid="{7B0B7F60-560F-4B1F-B64C-AA8BDB91C9E9}"/>
-    <hyperlink ref="B44" r:id="rId62" tooltip="乌西雅" xr:uid="{1C6894EC-3E15-4DA4-A1C4-F52FD29F7DD1}"/>
-    <hyperlink ref="B51" r:id="rId63" xr:uid="{5C1AD448-908F-4674-8DBF-FE78ACDAD13A}"/>
-    <hyperlink ref="E38" r:id="rId64" tooltip="拿单 (大卫之子)" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E5%8D%95_(%E5%A4%A7%E5%8D%AB%E4%B9%8B%E5%AD%90)" xr:uid="{92E3C8CE-5A0E-454E-BB57-BC9442223C07}"/>
+    <hyperlink ref="F54" r:id="rId1" location="%E6%89%80%E7%BD%97%E5%B7%B4%E4%BC%AF%E7%9A%84%E5%84%BF%E5%AD%90" display="耶稣的谱系#所罗巴伯的儿子" xr:uid="{54F552CE-A939-493B-8918-9063DDDF512C}"/>
+    <hyperlink ref="E43" r:id="rId2" tooltip="约兰 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E8%98%AD_(%E7%8C%B6%E5%A4%A7)" xr:uid="{52C2BA8B-5ECE-42B9-9E6C-A04B094B3B9E}"/>
+    <hyperlink ref="E42" r:id="rId3" tooltip="约沙法" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E6%B2%99%E6%B3%95" xr:uid="{B59F982E-DD72-467C-8B00-AAA40331BBC9}"/>
+    <hyperlink ref="E41" r:id="rId4" tooltip="亚撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E6%92%92" xr:uid="{A676C111-98F8-4E28-8611-1BDF1FC30B26}"/>
+    <hyperlink ref="E40" r:id="rId5" tooltip="亚比央" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E6%AF%94%E5%A4%AE" xr:uid="{57C451CF-E122-4EC6-9EFD-528D899E3F29}"/>
+    <hyperlink ref="E39" r:id="rId6" tooltip="罗波安" display="https://zh.wikipedia.org/wiki/%E7%BE%85%E6%B3%A2%E5%AE%89" xr:uid="{4D227C43-BBFE-41B2-8B88-F2708BB888E3}"/>
+    <hyperlink ref="E38" r:id="rId7" tooltip="所罗门 (君王)" display="https://zh.wikipedia.org/wiki/%E6%89%80%E7%BE%85%E9%96%80_(%E5%90%9B%E7%8E%8B)" xr:uid="{F89BBBD8-3B29-4041-9F50-C47E1FC9DDED}"/>
+    <hyperlink ref="E37" r:id="rId8" tooltip="大卫王" display="https://zh.wikipedia.org/wiki/%E5%A4%A7%E8%A1%9B%E7%8E%8B" xr:uid="{56A7D6C7-26AA-47DA-85B6-7F89B92C4DD8}"/>
+    <hyperlink ref="E24" r:id="rId9" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{AB26EAD3-2D25-446C-B7DF-D9AC554B887C}"/>
+    <hyperlink ref="E25" r:id="rId10" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{F2B42AF0-FDFD-4B2C-9F9F-8C45A36138F3}"/>
+    <hyperlink ref="E26" r:id="rId11" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{77651F01-29D9-4DCB-848D-E80E8C560788}"/>
+    <hyperlink ref="E27" r:id="rId12" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{E90359D2-4200-458A-BC2A-55AEBB996A43}"/>
+    <hyperlink ref="E28" r:id="rId13" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{4E5C2745-ACD5-4C74-A5F5-4FD837AFAE30}"/>
+    <hyperlink ref="E29" r:id="rId14" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{5A9A3FA2-4296-48EE-8C43-C291D44CA4A2}"/>
+    <hyperlink ref="E30" r:id="rId15" tooltip="亚兰" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E5%85%B0" xr:uid="{83896BBE-33B4-430A-A9D6-027F40A5EF56}"/>
+    <hyperlink ref="E31" r:id="rId16" tooltip="亚米拿达" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E7%B1%B3%E6%8B%BF%E8%BE%BE" xr:uid="{AD76F7C8-8520-4820-8E59-5F7949882E07}"/>
+    <hyperlink ref="E32" r:id="rId17" tooltip="拿顺" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%A1%BA" xr:uid="{3D372BF3-E2B4-48C4-994F-3EA8F87944C7}"/>
+    <hyperlink ref="E33" r:id="rId18" tooltip="撒门" display="https://zh.wikipedia.org/wiki/%E6%92%92%E9%97%A8" xr:uid="{E5213FF4-5133-432C-B833-690A5DCFBDAC}"/>
+    <hyperlink ref="E34" r:id="rId19" tooltip="波阿斯" display="https://zh.wikipedia.org/wiki/%E6%B3%A2%E9%98%BF%E6%96%AF" xr:uid="{B10BBF17-640C-4F13-BF71-029201BF677D}"/>
+    <hyperlink ref="E35" r:id="rId20" tooltip="俄备得" display="https://zh.wikipedia.org/wiki/%E4%BF%84%E5%A4%87%E5%BE%97" xr:uid="{511B802D-143F-4476-BE02-789D35011D3B}"/>
+    <hyperlink ref="E36" r:id="rId21" tooltip="耶西" display="https://zh.wikipedia.org/wiki/%E8%80%B6%E8%A5%BF" xr:uid="{640F03ED-E19C-444F-B433-04003D895D45}"/>
+    <hyperlink ref="H37" r:id="rId22" tooltip="大卫王" display="https://zh.wikipedia.org/wiki/%E5%A4%A7%E8%A1%9B%E7%8E%8B" xr:uid="{AC65AEF8-5BC2-432B-99E3-1B237ECEDF85}"/>
+    <hyperlink ref="H4" r:id="rId23" tooltip="亚当" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E7%95%B6" xr:uid="{FF35CB0F-ADF7-4440-A7E4-012E5A5926CF}"/>
+    <hyperlink ref="H5" r:id="rId24" tooltip="塞特" display="https://zh.wikipedia.org/wiki/%E5%A1%9E%E7%89%B9" xr:uid="{9169DB06-65EB-4C01-AB8F-9EEEA0793CAB}"/>
+    <hyperlink ref="H6" r:id="rId25" tooltip="以挪士" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%8C%AA%E5%A3%AB" xr:uid="{1ADEE73F-6EE5-4F42-8A99-309C0390CF17}"/>
+    <hyperlink ref="H7" r:id="rId26" tooltip="该南" display="https://zh.wikipedia.org/wiki/%E8%AF%A5%E5%8D%97" xr:uid="{4B3359C4-3F44-4215-8F0A-7214B391D814}"/>
+    <hyperlink ref="H8" r:id="rId27" tooltip="玛勒列" display="https://zh.wikipedia.org/wiki/%E7%8E%9B%E5%8B%92%E5%88%97" xr:uid="{95351270-C25C-49CF-A2AC-8B7154C90EED}"/>
+    <hyperlink ref="H9" r:id="rId28" tooltip="雅列" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%88%97" xr:uid="{ACEC4366-E2A2-49D9-A83C-49F1C0CE6540}"/>
+    <hyperlink ref="H10" r:id="rId29" tooltip="以诺" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E8%AB%BE" xr:uid="{3447F6F4-A1AB-4F5E-A201-6BE4B222437A}"/>
+    <hyperlink ref="H11" r:id="rId30" tooltip="玛土撒拉" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E5%9C%9F%E6%92%92%E6%8B%89" xr:uid="{45D2DB60-9AED-45B2-AD66-B5B37EC8E712}"/>
+    <hyperlink ref="H12" r:id="rId31" tooltip="拉麦" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E9%BA%A6" xr:uid="{41E2BE11-4D08-431B-9BD6-3236655F5255}"/>
+    <hyperlink ref="H13" r:id="rId32" tooltip="挪亚" display="https://zh.wikipedia.org/wiki/%E6%8C%AA%E4%BA%9E" xr:uid="{79F73FE6-51FD-4324-9AAD-16135AB1DD8B}"/>
+    <hyperlink ref="H14" r:id="rId33" tooltip="闪 (圣经)" display="https://zh.wikipedia.org/wiki/%E9%96%83_(%E8%81%96%E7%B6%93)" xr:uid="{84177492-4E71-4A6E-82EB-9099408F9F54}"/>
+    <hyperlink ref="H15" r:id="rId34" tooltip="亚法撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E6%B3%95%E6%92%92" xr:uid="{233F9479-DCA3-4915-8187-63F1001850F5}"/>
+    <hyperlink ref="H17" r:id="rId35" tooltip="沙拉 (圣经人物)" display="https://zh.wikipedia.org/wiki/%E6%B2%99%E6%8B%89_(%E5%9C%A3%E7%BB%8F%E4%BA%BA%E7%89%A9)" xr:uid="{0E57A2B1-02AC-4283-BEE9-29E6311064C4}"/>
+    <hyperlink ref="H18" r:id="rId36" tooltip="希伯" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E4%BC%AF" xr:uid="{534809CC-247C-46D1-B2E4-CED8F44B17DA}"/>
+    <hyperlink ref="H19" r:id="rId37" tooltip="法勒" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92" xr:uid="{6DE726CE-F659-499C-AAFC-6343784BADFE}"/>
+    <hyperlink ref="H20" r:id="rId38" tooltip="拉吴" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E5%90%B4" xr:uid="{E682953A-CD35-4E2F-942C-B4ED6682DDAE}"/>
+    <hyperlink ref="H21" r:id="rId39" tooltip="西鹿" display="https://zh.wikipedia.org/wiki/%E8%A5%BF%E9%B9%BF" xr:uid="{D42A9EA5-BA38-4053-B37D-EE22C85DB73D}"/>
+    <hyperlink ref="H22" r:id="rId40" tooltip="拿鹤" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%B9%A4" xr:uid="{CA8B6393-8FED-4235-B3A5-21B9255D0DE1}"/>
+    <hyperlink ref="H23" r:id="rId41" tooltip="他拉" display="https://zh.wikipedia.org/wiki/%E4%BB%96%E6%8B%89" xr:uid="{C2994B2D-1F9B-492E-8F29-BC298694C868}"/>
+    <hyperlink ref="H24" r:id="rId42" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{63D8363D-B530-4CF6-91F3-BD042ECCAC8D}"/>
+    <hyperlink ref="H25" r:id="rId43" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{70B7F414-BB95-4A8C-9A3D-6E291A34A1F9}"/>
+    <hyperlink ref="H26" r:id="rId44" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{2860D780-F11A-4C03-AD36-27B400A33726}"/>
+    <hyperlink ref="H27" r:id="rId45" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{6CBA7CED-39C8-48D6-8C75-76669537007A}"/>
+    <hyperlink ref="H28" r:id="rId46" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{E83B196D-0180-497D-AE5C-B7F21D9146DF}"/>
+    <hyperlink ref="H29" r:id="rId47" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{0E3BB2A0-C600-4754-B61E-66995A4F2BF5}"/>
+    <hyperlink ref="H30" r:id="rId48" tooltip="亚兰" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E5%85%B0" xr:uid="{7DB98F20-15A9-44C4-A04C-446DCBF285FF}"/>
+    <hyperlink ref="H31" r:id="rId49" tooltip="亚米拿达" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E7%B1%B3%E6%8B%BF%E8%BE%BE" xr:uid="{7AA27047-62D6-4044-9E49-2D7AD0967610}"/>
+    <hyperlink ref="H32" r:id="rId50" tooltip="拿顺" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%A1%BA" xr:uid="{1FB7A8C9-6415-4379-90F0-F65A5F10588F}"/>
+    <hyperlink ref="H33" r:id="rId51" tooltip="撒门" display="https://zh.wikipedia.org/wiki/%E6%92%92%E9%97%A8" xr:uid="{C9542CC7-3E57-4474-9867-5356C40CAC08}"/>
+    <hyperlink ref="H34" r:id="rId52" tooltip="波阿斯" display="https://zh.wikipedia.org/wiki/%E6%B3%A2%E9%98%BF%E6%96%AF" xr:uid="{5C9F88C7-B2BE-4A57-8A14-D37A10C149B7}"/>
+    <hyperlink ref="H35" r:id="rId53" tooltip="俄备得" display="https://zh.wikipedia.org/wiki/%E4%BF%84%E5%A4%87%E5%BE%97" xr:uid="{2ACE66BD-AFA7-4C5A-B203-8D789A3528ED}"/>
+    <hyperlink ref="H36" r:id="rId54" tooltip="耶西" display="https://zh.wikipedia.org/wiki/%E8%80%B6%E8%A5%BF" xr:uid="{779E1BF0-8B9C-47B9-9FFA-DEE550B98674}"/>
+    <hyperlink ref="E50" r:id="rId55" tooltip="约西亚" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E8%A5%BF%E4%BA%9E" xr:uid="{4D696DF6-1005-44B3-86F4-90F920A861DC}"/>
+    <hyperlink ref="E49" r:id="rId56" tooltip="亚们" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%80%91" xr:uid="{E70AFC90-3B93-4F15-8176-EB01E1B80657}"/>
+    <hyperlink ref="E48" r:id="rId57" tooltip="玛拿西 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E6%8B%BF%E8%A5%BF_(%E7%8C%B6%E5%A4%A7)" xr:uid="{271247F8-BA63-4867-83BF-BAE0721A7A43}"/>
+    <hyperlink ref="E47" r:id="rId58" tooltip="希西家" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E8%A5%BF%E5%AE%B6" xr:uid="{B3E5C22E-6B7D-4620-B001-CB824FAA924E}"/>
+    <hyperlink ref="E46" r:id="rId59" tooltip="亚哈斯" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%93%88%E6%96%AF" xr:uid="{B153943D-19EF-4D83-965B-568A39FBA15F}"/>
+    <hyperlink ref="E45" r:id="rId60" tooltip="约坦" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E5%9D%A6" xr:uid="{404F7698-EB07-4F78-B8F7-2956FD0DCE1E}"/>
+    <hyperlink ref="E53" r:id="rId61" xr:uid="{7B0B7F60-560F-4B1F-B64C-AA8BDB91C9E9}"/>
+    <hyperlink ref="E44" r:id="rId62" tooltip="乌西雅" xr:uid="{1C6894EC-3E15-4DA4-A1C4-F52FD29F7DD1}"/>
+    <hyperlink ref="E51" r:id="rId63" xr:uid="{5C1AD448-908F-4674-8DBF-FE78ACDAD13A}"/>
+    <hyperlink ref="H38" r:id="rId64" tooltip="拿单 (大卫之子)" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E5%8D%95_(%E5%A4%A7%E5%8D%AB%E4%B9%8B%E5%AD%90)" xr:uid="{92E3C8CE-5A0E-454E-BB57-BC9442223C07}"/>
+    <hyperlink ref="B4" r:id="rId65" tooltip="亚当" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E7%95%B6" xr:uid="{686EC380-3758-4219-850F-B2573EED0467}"/>
+    <hyperlink ref="B5" r:id="rId66" tooltip="塞特" display="https://zh.wikipedia.org/wiki/%E5%A1%9E%E7%89%B9" xr:uid="{2E3F44B8-1BE0-4149-8044-F674D53DE0FC}"/>
+    <hyperlink ref="B6" r:id="rId67" tooltip="以挪士" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%8C%AA%E5%A3%AB" xr:uid="{D55463C1-629B-4B8E-B27D-F9509C198791}"/>
+    <hyperlink ref="B7" r:id="rId68" tooltip="该南" display="https://zh.wikipedia.org/wiki/%E8%AF%A5%E5%8D%97" xr:uid="{44E7A10C-8006-404E-902B-B879D3E8BE91}"/>
+    <hyperlink ref="B8" r:id="rId69" tooltip="玛勒列" display="https://zh.wikipedia.org/wiki/%E7%8E%9B%E5%8B%92%E5%88%97" xr:uid="{B0A991AA-BA00-4886-8375-3866C91BF7C9}"/>
+    <hyperlink ref="B9" r:id="rId70" tooltip="雅列" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%88%97" xr:uid="{166E0404-D2C1-4964-BE55-FB26474FEDF8}"/>
+    <hyperlink ref="B10" r:id="rId71" tooltip="以诺" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E8%AB%BE" xr:uid="{128236EE-A33E-49F7-9916-6546AA7F3E71}"/>
+    <hyperlink ref="B11" r:id="rId72" tooltip="玛土撒拉" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E5%9C%9F%E6%92%92%E6%8B%89" xr:uid="{546DA490-7DEA-4515-A600-274DEE027ECB}"/>
+    <hyperlink ref="B12" r:id="rId73" tooltip="拉麦" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E9%BA%A6" xr:uid="{937345C6-3955-4C83-8562-18A94CADB372}"/>
+    <hyperlink ref="B13" r:id="rId74" tooltip="挪亚" display="https://zh.wikipedia.org/wiki/%E6%8C%AA%E4%BA%9E" xr:uid="{90CBFDA1-CED2-4431-AAD2-6089017A8F63}"/>
+    <hyperlink ref="B14" r:id="rId75" tooltip="闪 (圣经)" display="https://zh.wikipedia.org/wiki/%E9%96%83_(%E8%81%96%E7%B6%93)" xr:uid="{CCC9280C-5E78-4AE7-BDDB-9BD2710E2AF7}"/>
+    <hyperlink ref="B15" r:id="rId76" tooltip="亚法撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E6%B3%95%E6%92%92" xr:uid="{C8E15ADE-B5B5-4881-BFD9-6EE0231D17D6}"/>
+    <hyperlink ref="B17" r:id="rId77" tooltip="沙拉 (圣经人物)" display="https://zh.wikipedia.org/wiki/%E6%B2%99%E6%8B%89_(%E5%9C%A3%E7%BB%8F%E4%BA%BA%E7%89%A9)" xr:uid="{F623895D-8BC1-4E53-843E-9E375E2F4A99}"/>
+    <hyperlink ref="B18" r:id="rId78" tooltip="希伯" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E4%BC%AF" xr:uid="{0BB9151E-7A8D-4423-9A84-FB8F03985037}"/>
+    <hyperlink ref="B19" r:id="rId79" tooltip="法勒" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92" xr:uid="{3551A306-AA2F-4CEE-A062-3B4BBBD117FD}"/>
+    <hyperlink ref="B20" r:id="rId80" tooltip="拉吴" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E5%90%B4" xr:uid="{64ECE156-E51F-4204-9A1E-B69F41ECE150}"/>
+    <hyperlink ref="B21" r:id="rId81" tooltip="西鹿" display="https://zh.wikipedia.org/wiki/%E8%A5%BF%E9%B9%BF" xr:uid="{421F4ADD-DB7C-4DB8-933B-CFC005303684}"/>
+    <hyperlink ref="B22" r:id="rId82" tooltip="拿鹤" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%B9%A4" xr:uid="{3A6A833E-6CCA-426D-BACB-EFC7CEDC0C5F}"/>
+    <hyperlink ref="B23" r:id="rId83" tooltip="他拉" display="https://zh.wikipedia.org/wiki/%E4%BB%96%E6%8B%89" xr:uid="{980EFDAD-81E6-4F88-8487-32337CD055B1}"/>
+    <hyperlink ref="B24" r:id="rId84" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{73264DE7-3452-45F3-B152-873A1C4D6B78}"/>
+    <hyperlink ref="B25" r:id="rId85" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{ACFB9A22-6CEB-4FAA-82A2-149FC3A7411B}"/>
+    <hyperlink ref="B26" r:id="rId86" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{D4098122-6EB7-4374-895F-3878995D434F}"/>
+    <hyperlink ref="B27" r:id="rId87" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{35E7190F-8175-49E0-98EF-0EC451FF7D0A}"/>
+    <hyperlink ref="B28" r:id="rId88" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{1A901BFA-614C-4DED-9B55-148494546B91}"/>
+    <hyperlink ref="B29" r:id="rId89" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{BCD126EB-6C4B-4A9B-A944-E10162A59054}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId90"/>
 </worksheet>
 </file>
 
@@ -2246,20 +2594,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="2:5" ht="28" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2276,11 +2624,11 @@
       <c r="B4" s="2">
         <v>0</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="24" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="33" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2288,111 +2636,111 @@
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="24" t="s">
         <v>97</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="39"/>
+      <c r="E5" s="34"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="24" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="39"/>
+      <c r="E6" s="34"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>3</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="24" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="39"/>
+      <c r="E7" s="34"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>4</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="24" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="39"/>
+      <c r="E8" s="34"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="39"/>
+      <c r="E9" s="34"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>6</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="39"/>
+      <c r="E10" s="34"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>7</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>98</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="39"/>
+      <c r="E11" s="34"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>8</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="39"/>
+      <c r="E12" s="34"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>9</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="39"/>
+      <c r="E13" s="34"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>10</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="39"/>
+      <c r="E14" s="34"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>11</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="24" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="39"/>
+      <c r="E15" s="34"/>
     </row>
     <row r="16" spans="2:5" ht="28" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
@@ -2404,447 +2752,447 @@
       <c r="D16" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="39"/>
+      <c r="E16" s="34"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>13</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="24" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="39"/>
+      <c r="E17" s="34"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>14</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="24" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="39"/>
+      <c r="E18" s="34"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>15</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="24" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="39"/>
+      <c r="E19" s="34"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>16</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="24" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="39"/>
+      <c r="E20" s="34"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>17</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="24" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="39"/>
+      <c r="E21" s="34"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>18</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="24" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="39"/>
+      <c r="E22" s="34"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>19</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="24" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="2"/>
-      <c r="E23" s="39"/>
+      <c r="E23" s="34"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>20</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="24" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="39"/>
+      <c r="E24" s="34"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>21</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="24" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="39"/>
+      <c r="E25" s="34"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>22</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="24" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="39"/>
+      <c r="E26" s="34"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>23</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="24" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="39"/>
+      <c r="E27" s="34"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>24</v>
       </c>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="24" t="s">
         <v>22</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="39"/>
+      <c r="E28" s="34"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>25</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="24" t="s">
         <v>99</v>
       </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="39"/>
+      <c r="E29" s="34"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>26</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="24" t="s">
         <v>23</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="39"/>
+      <c r="E30" s="34"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>27</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="24" t="s">
         <v>24</v>
       </c>
       <c r="D31" s="2"/>
-      <c r="E31" s="39"/>
+      <c r="E31" s="34"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>28</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="24" t="s">
         <v>25</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="39"/>
+      <c r="E32" s="34"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>29</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="24" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="39"/>
+      <c r="E33" s="34"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <v>30</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="24" t="s">
         <v>27</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="39"/>
+      <c r="E34" s="34"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <v>31</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="24" t="s">
         <v>28</v>
       </c>
       <c r="D35" s="2"/>
-      <c r="E35" s="39"/>
+      <c r="E35" s="34"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <v>32</v>
       </c>
-      <c r="C36" s="25" t="s">
+      <c r="C36" s="24" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="39"/>
+      <c r="E36" s="34"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="13">
+      <c r="B37" s="12">
         <v>33</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="39"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="34"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <v>34</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="14" t="s">
         <v>32</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="39"/>
+      <c r="E38" s="34"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="13">
+      <c r="B39" s="12">
         <v>35</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="39"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="34"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <v>36</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="15" t="s">
         <v>86</v>
       </c>
       <c r="D40" s="2"/>
-      <c r="E40" s="39"/>
+      <c r="E40" s="34"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="13">
+      <c r="B41" s="12">
         <v>37</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="39"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="34"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <v>38</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="14" t="s">
         <v>38</v>
       </c>
       <c r="D42" s="2"/>
-      <c r="E42" s="39"/>
+      <c r="E42" s="34"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="13">
+      <c r="B43" s="12">
         <v>39</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="39"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="34"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>40</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="15" t="s">
         <v>74</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="39"/>
+      <c r="E44" s="34"/>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B45" s="13">
+      <c r="B45" s="12">
         <v>41</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="14" t="s">
         <v>83</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E45" s="39"/>
+      <c r="E45" s="34"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>42</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="14" t="s">
         <v>84</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E46" s="39"/>
+      <c r="E46" s="34"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B47" s="13">
+      <c r="B47" s="12">
         <v>43</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="39"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="34"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>44</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="14" t="s">
         <v>42</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="39"/>
+      <c r="E48" s="34"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="13">
+      <c r="B49" s="12">
         <v>45</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="39"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="34"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>46</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="15" t="s">
         <v>100</v>
       </c>
       <c r="D50" s="2"/>
-      <c r="E50" s="39"/>
+      <c r="E50" s="34"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="13">
+      <c r="B51" s="12">
         <v>47</v>
       </c>
-      <c r="C51" s="15" t="s">
+      <c r="C51" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="39"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="34"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="21">
+      <c r="B52" s="20">
         <v>48</v>
       </c>
-      <c r="C52" s="15" t="s">
+      <c r="C52" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D52" s="22"/>
-      <c r="E52" s="39"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="34"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="13">
+      <c r="B53" s="12">
         <v>49</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D53" s="14"/>
-      <c r="E53" s="39"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="34"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="21">
+      <c r="B54" s="20">
         <v>50</v>
       </c>
-      <c r="C54" s="15" t="s">
+      <c r="C54" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D54" s="23" t="s">
+      <c r="D54" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="E54" s="39"/>
+      <c r="E54" s="34"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="13">
+      <c r="B55" s="12">
         <v>51</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="D55" s="14"/>
-      <c r="E55" s="39"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="34"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="13">
+      <c r="B56" s="12">
         <v>52</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D56" s="23" t="s">
+      <c r="D56" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="E56" s="39"/>
+      <c r="E56" s="34"/>
     </row>
     <row r="57" spans="2:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="B57" s="21">
+      <c r="B57" s="20">
         <v>53</v>
       </c>
-      <c r="C57" s="15" t="s">
+      <c r="C57" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D57" s="24" t="s">
+      <c r="D57" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="E57" s="39"/>
-      <c r="F57" s="28"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="27"/>
     </row>
     <row r="58" spans="2:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="B58" s="13">
+      <c r="B58" s="12">
         <v>54</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="D58" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E58" s="38" t="s">
+      <c r="E58" s="33" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="13">
+      <c r="B59" s="12">
         <v>55</v>
       </c>
       <c r="C59" s="6" t="s">
@@ -2853,7 +3201,7 @@
       <c r="D59" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E59" s="39"/>
+      <c r="E59" s="34"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
@@ -2865,10 +3213,10 @@
       <c r="D60" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E60" s="39"/>
+      <c r="E60" s="34"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="13">
+      <c r="B61" s="12">
         <v>57</v>
       </c>
       <c r="C61" s="6" t="s">
@@ -2877,10 +3225,10 @@
       <c r="D61" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="39"/>
+      <c r="E61" s="34"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="13">
+      <c r="B62" s="12">
         <v>58</v>
       </c>
       <c r="C62" s="6" t="s">
@@ -2889,7 +3237,7 @@
       <c r="D62" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E62" s="39"/>
+      <c r="E62" s="34"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="2">
@@ -2901,10 +3249,10 @@
       <c r="D63" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E63" s="39"/>
+      <c r="E63" s="34"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="13">
+      <c r="B64" s="12">
         <v>60</v>
       </c>
       <c r="C64" s="6" t="s">
@@ -2913,10 +3261,10 @@
       <c r="D64" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E64" s="39"/>
+      <c r="E64" s="34"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B65" s="13">
+      <c r="B65" s="12">
         <v>61</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -2925,7 +3273,7 @@
       <c r="D65" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E65" s="39"/>
+      <c r="E65" s="34"/>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="2">
@@ -2937,10 +3285,10 @@
       <c r="D66" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E66" s="39"/>
+      <c r="E66" s="34"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B67" s="13">
+      <c r="B67" s="12">
         <v>63</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -2949,10 +3297,10 @@
       <c r="D67" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E67" s="39"/>
+      <c r="E67" s="34"/>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B68" s="13">
+      <c r="B68" s="12">
         <v>64</v>
       </c>
       <c r="C68" s="2" t="s">

--- a/其它格式未转换/耶稣家谱/耶稣家谱.xlsx
+++ b/其它格式未转换/耶稣家谱/耶稣家谱.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文件\notes\其它格式未转换\耶稣家谱\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E71BEC3A-574A-4AC6-AF0F-99FB594F3B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEF5734-8F00-44BD-A5EC-AAB2C0670690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="圣经原文" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="125">
   <si>
     <t>神</t>
   </si>
@@ -152,104 +152,56 @@
     <t>约坦</t>
   </si>
   <si>
-    <t>西缅</t>
-  </si>
-  <si>
     <t>亚哈斯</t>
   </si>
   <si>
     <t>利末</t>
   </si>
   <si>
-    <t>玛塔</t>
-  </si>
-  <si>
     <t>玛拿西</t>
   </si>
   <si>
-    <t>约令</t>
-  </si>
-  <si>
     <t>亚们</t>
   </si>
   <si>
-    <t>以利以谢</t>
-  </si>
-  <si>
     <t>约西亚</t>
   </si>
   <si>
-    <t>约细</t>
-  </si>
-  <si>
-    <t>珥</t>
+    <t>麦基</t>
+  </si>
+  <si>
+    <t>以律</t>
+  </si>
+  <si>
+    <t>马但</t>
+  </si>
+  <si>
+    <t>耶稣</t>
+  </si>
+  <si>
+    <t>玛他提雅</t>
+  </si>
+  <si>
+    <t>拿该</t>
+  </si>
+  <si>
+    <t>以斯利</t>
+  </si>
+  <si>
+    <t>拿鸿</t>
+  </si>
+  <si>
+    <t>亚摩斯</t>
+  </si>
+  <si>
+    <t>雅拿</t>
+  </si>
+  <si>
+    <t>亚哈谢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>撒拉铁</t>
-  </si>
-  <si>
-    <t>以摩当</t>
-  </si>
-  <si>
-    <t>所罗巴伯</t>
-  </si>
-  <si>
-    <t>哥桑</t>
-  </si>
-  <si>
-    <t>亚底</t>
-  </si>
-  <si>
-    <t>麦基</t>
-  </si>
-  <si>
-    <t>尼利</t>
-  </si>
-  <si>
-    <t>以律</t>
-  </si>
-  <si>
-    <t>利撒</t>
-  </si>
-  <si>
-    <t>约亚拿</t>
-  </si>
-  <si>
-    <t>马但</t>
-  </si>
-  <si>
-    <t>西美</t>
-  </si>
-  <si>
-    <t>耶稣</t>
-  </si>
-  <si>
-    <t>玛他提雅</t>
-  </si>
-  <si>
-    <t>玛押</t>
-  </si>
-  <si>
-    <t>拿该</t>
-  </si>
-  <si>
-    <t>以斯利</t>
-  </si>
-  <si>
-    <t>拿鸿</t>
-  </si>
-  <si>
-    <t>亚摩斯</t>
-  </si>
-  <si>
-    <t>雅拿</t>
-  </si>
-  <si>
-    <t>亚哈谢</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>撒拉铁</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -258,10 +210,6 @@
   </si>
   <si>
     <t>人物</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亚当的第 n 世孙</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -356,7 +304,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>《马太福音1:9》乌西雅之前缺少四代王三代人：
+    <t>《马太福音1:11》约雅斤之前缺少两代王一代人：
+约哈斯：约西亚之子
+约雅敬：约西亚之子
+此处的约雅斤即为约雅敬之子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>乌西雅（亚撒利雅）</t>
+  </si>
+  <si>
+    <t>约雅斤（耶哥尼雅）</t>
+  </si>
+  <si>
+    <t>约雅斤的孙子
+毗大雅的儿子，撒拉铁的侄子
+利未婚给撒拉铁当儿子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毗大雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛达他</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有缺失</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>父传子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">14 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚法撒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《旧约》（创10:24）（历上1:18）引用的是希伯来原文，没有该南。
+《新约》（路加3:36）引用的是希腊文《七十士译本》，包含该南。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大卫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>创世纪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>《马太福音1:8》乌西雅之前缺少四代王三代人：
 亚哈谢：约兰之子
 亚她利雅：亚哈谢之母
 约阿施：亚哈谢之子
@@ -365,76 +369,196 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>《马太福音1:11》约雅斤之前缺少两代王一代人：
-约哈斯：约西亚之子
-约雅敬：约西亚之子
-此处的约雅斤即为约雅敬之子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《马太福音1:9》缺失</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《马太福音1:11》缺失</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>乌西雅（亚撒利雅）</t>
-  </si>
-  <si>
-    <t>约雅斤（耶哥尼雅）</t>
-  </si>
-  <si>
-    <t>《旧约》（创11:36）（历上1:18-25）引用的是希伯来原文，没有该南。
-《新约》（路加3:36）引用的是希腊文《七十士译本》，包含该南。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>约雅斤的孙子
-毗大雅的儿子，撒拉铁的侄子
+    <t>创11:13 和历上1:18 引用的是希伯来原文，没有该南。
+路加3:36 引用的是希腊文《七十士译本》，包含该南。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>犹大</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西缅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利末</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约令</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以利以谢</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约细</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>珥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以摩当</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哥桑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚底</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>麦基</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尼利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>利撒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约亚拿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>约瑟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛他提雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛押</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>太 1:8</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 缺失</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>太 1:11</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 缺失</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>此处依据</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="10"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>代上 3:17-19 整理</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>拉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3:2、该 1:1、太 1:12、路 3:27 中，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所罗巴伯均被称为撒拉铁的儿子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+代上 3:17-19 中，所罗巴伯被称为毗大雅的儿子
+约雅斤的孙子
+毗大雅的儿子
+撒拉铁的侄子
 利未婚给撒拉铁当儿子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>毗大雅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《马太福音1:11》写为撒拉铁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛达他</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有缺失</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>父传子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">14 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亚法撒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《旧约》（创10:24）（历上1:18）引用的是希伯来原文，没有该南。
-《新约》（路加3:36）引用的是希腊文《七十士译本》，包含该南。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大卫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>创世纪</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>血统存疑：
+代上 3:19 在列举所罗巴伯的孩子时，并未提到亚比玉。
+亚比玉在圣经中仅在太 1:13 中提到过一次</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,7 +566,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -488,6 +612,31 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="8">
@@ -616,7 +765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -653,9 +802,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -677,16 +823,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
@@ -707,6 +847,30 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -722,29 +886,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1036,67 +1182,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="42.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="A1" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="41"/>
-      <c r="B2" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="42" t="s">
-        <v>82</v>
+      <c r="A2" s="28"/>
+      <c r="B2" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>65</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35">
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27">
+        <v>1</v>
+      </c>
+      <c r="H3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="H3" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="I3" s="35"/>
+      <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="2"/>
@@ -1104,50 +1250,50 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2">
-        <v>0</v>
-      </c>
-      <c r="H4" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
-      <c r="B5" s="24" t="s">
-        <v>97</v>
+      <c r="B5" s="21" t="s">
+        <v>80</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2">
-        <v>1</v>
-      </c>
-      <c r="H5" s="24" t="s">
-        <v>97</v>
+        <v>3</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>80</v>
       </c>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2"/>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="24"/>
+      <c r="C6" s="21"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2">
-        <v>2</v>
-      </c>
-      <c r="H6" s="24" t="s">
+      <c r="G6" s="27">
+        <v>4</v>
+      </c>
+      <c r="H6" s="21" t="s">
         <v>2</v>
       </c>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="21" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="2"/>
@@ -1155,16 +1301,16 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2">
-        <v>3</v>
-      </c>
-      <c r="H7" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="21" t="s">
         <v>3</v>
       </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="21" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="2"/>
@@ -1172,33 +1318,33 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2">
-        <v>4</v>
-      </c>
-      <c r="H8" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H8" s="21" t="s">
         <v>4</v>
       </c>
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="21" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2">
-        <v>5</v>
-      </c>
-      <c r="H9" s="24" t="s">
+      <c r="G9" s="27">
+        <v>7</v>
+      </c>
+      <c r="H9" s="21" t="s">
         <v>5</v>
       </c>
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2"/>
@@ -1206,50 +1352,50 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2">
-        <v>6</v>
-      </c>
-      <c r="H10" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="21" t="s">
         <v>6</v>
       </c>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2"/>
-      <c r="B11" s="24" t="s">
-        <v>98</v>
+      <c r="B11" s="21" t="s">
+        <v>81</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2">
-        <v>7</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>98</v>
+        <v>9</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>81</v>
       </c>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2"/>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="21" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2">
-        <v>8</v>
-      </c>
-      <c r="H12" s="24" t="s">
+      <c r="G12" s="27">
+        <v>10</v>
+      </c>
+      <c r="H12" s="21" t="s">
         <v>7</v>
       </c>
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2"/>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="2"/>
@@ -1257,16 +1403,16 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2">
-        <v>9</v>
-      </c>
-      <c r="H13" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="21" t="s">
         <v>8</v>
       </c>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="21" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="2"/>
@@ -1274,54 +1420,54 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2">
-        <v>10</v>
-      </c>
-      <c r="H14" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="21" t="s">
         <v>9</v>
       </c>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="18" t="s">
-        <v>117</v>
+      <c r="B15" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2">
-        <v>11</v>
-      </c>
-      <c r="H15" s="18" t="s">
-        <v>117</v>
+      <c r="G15" s="27">
+        <v>13</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>95</v>
       </c>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" ht="84" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="56" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="2"/>
@@ -1329,33 +1475,33 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2">
-        <v>13</v>
-      </c>
-      <c r="H17" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="21" t="s">
         <v>11</v>
       </c>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2">
-        <v>14</v>
-      </c>
-      <c r="H18" s="24" t="s">
+      <c r="G18" s="27">
+        <v>16</v>
+      </c>
+      <c r="H18" s="21" t="s">
         <v>12</v>
       </c>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="21" t="s">
         <v>13</v>
       </c>
       <c r="C19" s="2"/>
@@ -1363,16 +1509,16 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2">
-        <v>15</v>
-      </c>
-      <c r="H19" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="21" t="s">
         <v>13</v>
       </c>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2"/>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="21" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="2"/>
@@ -1380,33 +1526,33 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2">
-        <v>16</v>
-      </c>
-      <c r="H20" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="21" t="s">
         <v>14</v>
       </c>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2"/>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2">
-        <v>17</v>
-      </c>
-      <c r="H21" s="24" t="s">
+      <c r="G21" s="27">
+        <v>19</v>
+      </c>
+      <c r="H21" s="21" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2"/>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2"/>
@@ -1414,16 +1560,16 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2">
-        <v>18</v>
-      </c>
-      <c r="H22" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="21" t="s">
         <v>16</v>
       </c>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2"/>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C23" s="2"/>
@@ -1431,136 +1577,136 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2">
-        <v>19</v>
-      </c>
-      <c r="H23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="21" t="s">
         <v>17</v>
       </c>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="21" t="s">
         <v>18</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="11">
         <v>1</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="21" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="3"/>
-      <c r="G24" s="2">
-        <v>20</v>
-      </c>
-      <c r="H24" s="24" t="s">
+      <c r="G24" s="27">
+        <v>22</v>
+      </c>
+      <c r="H24" s="21" t="s">
         <v>18</v>
       </c>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="21" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="11">
         <v>2</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="21" t="s">
         <v>19</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2">
-        <v>21</v>
-      </c>
-      <c r="H25" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="21" t="s">
         <v>19</v>
       </c>
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="21" t="s">
         <v>20</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="11">
         <v>3</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="21" t="s">
         <v>20</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2">
-        <v>22</v>
-      </c>
-      <c r="H26" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="21" t="s">
         <v>20</v>
       </c>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="21" t="s">
         <v>21</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="11">
         <v>4</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="21" t="s">
         <v>21</v>
       </c>
       <c r="F27" s="2"/>
-      <c r="G27" s="2">
-        <v>23</v>
-      </c>
-      <c r="H27" s="24" t="s">
+      <c r="G27" s="27">
+        <v>25</v>
+      </c>
+      <c r="H27" s="21" t="s">
         <v>21</v>
       </c>
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="21" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="11">
         <v>5</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="21" t="s">
         <v>22</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2">
-        <v>24</v>
-      </c>
-      <c r="H28" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="21" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="2"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
-      <c r="B29" s="24" t="s">
-        <v>99</v>
+      <c r="B29" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="11">
         <v>6</v>
       </c>
-      <c r="E29" s="24" t="s">
-        <v>99</v>
+      <c r="E29" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="F29" s="2"/>
       <c r="G29" s="2">
-        <v>25</v>
-      </c>
-      <c r="H29" s="24" t="s">
-        <v>99</v>
+        <v>27</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="I29" s="2"/>
     </row>
@@ -1571,14 +1717,14 @@
       <c r="D30" s="11">
         <v>7</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="21" t="s">
         <v>23</v>
       </c>
       <c r="F30" s="2"/>
-      <c r="G30" s="2">
-        <v>26</v>
-      </c>
-      <c r="H30" s="24" t="s">
+      <c r="G30" s="27">
+        <v>28</v>
+      </c>
+      <c r="H30" s="21" t="s">
         <v>23</v>
       </c>
       <c r="I30" s="2"/>
@@ -1590,14 +1736,14 @@
       <c r="D31" s="11">
         <v>8</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="21" t="s">
         <v>24</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2">
-        <v>27</v>
-      </c>
-      <c r="H31" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="21" t="s">
         <v>24</v>
       </c>
       <c r="I31" s="2"/>
@@ -1609,14 +1755,14 @@
       <c r="D32" s="11">
         <v>9</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="21" t="s">
         <v>25</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2">
-        <v>28</v>
-      </c>
-      <c r="H32" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="H32" s="21" t="s">
         <v>25</v>
       </c>
       <c r="I32" s="2"/>
@@ -1628,14 +1774,14 @@
       <c r="D33" s="11">
         <v>10</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="21" t="s">
         <v>26</v>
       </c>
       <c r="F33" s="2"/>
-      <c r="G33" s="2">
-        <v>29</v>
-      </c>
-      <c r="H33" s="24" t="s">
+      <c r="G33" s="27">
+        <v>31</v>
+      </c>
+      <c r="H33" s="21" t="s">
         <v>26</v>
       </c>
       <c r="I33" s="2"/>
@@ -1647,14 +1793,14 @@
       <c r="D34" s="11">
         <v>11</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="21" t="s">
         <v>27</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2">
-        <v>30</v>
-      </c>
-      <c r="H34" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="21" t="s">
         <v>27</v>
       </c>
       <c r="I34" s="2"/>
@@ -1666,14 +1812,14 @@
       <c r="D35" s="11">
         <v>12</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="21" t="s">
         <v>28</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2">
-        <v>31</v>
-      </c>
-      <c r="H35" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="21" t="s">
         <v>28</v>
       </c>
       <c r="I35" s="2"/>
@@ -1685,14 +1831,14 @@
       <c r="D36" s="11">
         <v>13</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="21" t="s">
         <v>29</v>
       </c>
       <c r="F36" s="2"/>
-      <c r="G36" s="2">
-        <v>32</v>
-      </c>
-      <c r="H36" s="24" t="s">
+      <c r="G36" s="27">
+        <v>34</v>
+      </c>
+      <c r="H36" s="21" t="s">
         <v>29</v>
       </c>
       <c r="I36" s="2"/>
@@ -1702,17 +1848,17 @@
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="D37" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="22" t="s">
         <v>30</v>
       </c>
       <c r="F37" s="4"/>
       <c r="G37" s="4">
-        <v>33</v>
-      </c>
-      <c r="H37" s="29" t="s">
-        <v>119</v>
+        <v>35</v>
+      </c>
+      <c r="H37" s="26" t="s">
+        <v>97</v>
       </c>
       <c r="I37" s="4"/>
     </row>
@@ -1723,14 +1869,14 @@
       <c r="D38" s="11">
         <v>2</v>
       </c>
-      <c r="E38" s="14" t="s">
+      <c r="E38" s="13" t="s">
         <v>32</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="2">
-        <v>34</v>
-      </c>
-      <c r="H38" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="H38" s="18" t="s">
         <v>31</v>
       </c>
       <c r="I38" s="3"/>
@@ -1742,15 +1888,15 @@
       <c r="D39" s="11">
         <v>3</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="E39" s="13" t="s">
         <v>33</v>
       </c>
       <c r="F39" s="2"/>
-      <c r="G39" s="2">
-        <v>35</v>
+      <c r="G39" s="27">
+        <v>37</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="I39" s="2"/>
     </row>
@@ -1761,12 +1907,12 @@
       <c r="D40" s="11">
         <v>4</v>
       </c>
-      <c r="E40" s="15" t="s">
-        <v>86</v>
+      <c r="E40" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>34</v>
@@ -1780,12 +1926,12 @@
       <c r="D41" s="11">
         <v>5</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="13" t="s">
         <v>36</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>35</v>
@@ -1799,12 +1945,12 @@
       <c r="D42" s="11">
         <v>6</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" s="13" t="s">
         <v>38</v>
       </c>
       <c r="F42" s="2"/>
-      <c r="G42" s="2">
-        <v>38</v>
+      <c r="G42" s="27">
+        <v>40</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>37</v>
@@ -1818,12 +1964,12 @@
       <c r="D43" s="11">
         <v>7</v>
       </c>
-      <c r="E43" s="14" t="s">
+      <c r="E43" s="13" t="s">
         <v>40</v>
       </c>
       <c r="F43" s="6"/>
       <c r="G43" s="2">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>39</v>
@@ -1837,14 +1983,14 @@
       <c r="D44" s="11">
         <v>8</v>
       </c>
-      <c r="E44" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="F44" s="26" t="s">
-        <v>103</v>
+      <c r="E44" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F44" s="23" t="s">
+        <v>99</v>
       </c>
       <c r="G44" s="2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>41</v>
@@ -1858,15 +2004,15 @@
       <c r="D45" s="11">
         <v>9</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" s="13" t="s">
         <v>42</v>
       </c>
       <c r="F45" s="2"/>
-      <c r="G45" s="2">
-        <v>41</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>21</v>
+      <c r="G45" s="27">
+        <v>43</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="I45" s="2"/>
     </row>
@@ -1877,15 +2023,15 @@
       <c r="D46" s="11">
         <v>10</v>
       </c>
-      <c r="E46" s="14" t="s">
-        <v>44</v>
+      <c r="E46" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2">
-        <v>42</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="I46" s="2"/>
     </row>
@@ -1896,15 +2042,15 @@
       <c r="D47" s="11">
         <v>11</v>
       </c>
-      <c r="E47" s="15" t="s">
-        <v>100</v>
+      <c r="E47" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2">
-        <v>43</v>
-      </c>
-      <c r="H47" s="2" t="s">
         <v>45</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="I47" s="2"/>
     </row>
@@ -1915,17 +2061,17 @@
       <c r="D48" s="11">
         <v>12</v>
       </c>
-      <c r="E48" s="14" t="s">
-        <v>47</v>
+      <c r="E48" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="F48" s="2"/>
-      <c r="G48" s="2">
-        <v>44</v>
-      </c>
-      <c r="H48" s="2" t="s">
+      <c r="G48" s="27">
         <v>46</v>
       </c>
-      <c r="I48" s="2"/>
+      <c r="H48" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I48" s="6"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2"/>
@@ -1934,15 +2080,15 @@
       <c r="D49" s="11">
         <v>13</v>
       </c>
-      <c r="E49" s="14" t="s">
-        <v>49</v>
+      <c r="E49" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2">
-        <v>45</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="I49" s="2"/>
     </row>
@@ -1951,17 +2097,17 @@
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="E50" s="14" t="s">
-        <v>51</v>
+        <v>94</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2">
-        <v>46</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="I50" s="2"/>
     </row>
@@ -1972,17 +2118,17 @@
       <c r="D51" s="11">
         <v>1</v>
       </c>
-      <c r="E51" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="F51" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="G51" s="2">
-        <v>47</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>52</v>
+      <c r="E51" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G51" s="27">
+        <v>49</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="I51" s="2"/>
     </row>
@@ -1994,14 +2140,14 @@
         <v>2</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="F52" s="6"/>
       <c r="G52" s="2">
-        <v>48</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="I52" s="2"/>
     </row>
@@ -2012,17 +2158,17 @@
       <c r="D53" s="11">
         <v>3</v>
       </c>
-      <c r="E53" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="F53" s="23" t="s">
-        <v>110</v>
+      <c r="E53" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F53" s="20" t="s">
+        <v>89</v>
       </c>
       <c r="G53" s="2">
-        <v>49</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="I53" s="2"/>
     </row>
@@ -2034,16 +2180,16 @@
         <v>4</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="G54" s="2">
-        <v>50</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="27">
+        <v>52</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="I54" s="2"/>
     </row>
@@ -2055,16 +2201,16 @@
         <v>5</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G55" s="2">
-        <v>51</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="I55" s="2"/>
     </row>
@@ -2076,16 +2222,16 @@
         <v>6</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G56" s="2">
-        <v>52</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="I56" s="2"/>
     </row>
@@ -2097,16 +2243,16 @@
         <v>7</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G57" s="2">
-        <v>53</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>60</v>
+        <v>75</v>
+      </c>
+      <c r="G57" s="27">
+        <v>55</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="I57" s="2"/>
     </row>
@@ -2118,16 +2264,16 @@
         <v>8</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G58" s="2">
-        <v>54</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="I58" s="2"/>
     </row>
@@ -2139,16 +2285,16 @@
         <v>9</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G59" s="2">
-        <v>55</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="I59" s="2"/>
     </row>
@@ -2160,16 +2306,16 @@
         <v>10</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G60" s="2">
-        <v>56</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
+      </c>
+      <c r="G60" s="27">
+        <v>58</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="I60" s="2"/>
     </row>
@@ -2181,16 +2327,16 @@
         <v>11</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G61" s="2">
-        <v>57</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="I61" s="2"/>
     </row>
@@ -2205,13 +2351,13 @@
         <v>20</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G62" s="2">
-        <v>58</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>21</v>
+        <v>60</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="I62" s="2"/>
     </row>
@@ -2222,17 +2368,17 @@
       <c r="D63" s="11">
         <v>13</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E63" s="13" t="s">
         <v>41</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G63" s="2">
-        <v>59</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>41</v>
+        <v>75</v>
+      </c>
+      <c r="G63" s="27">
+        <v>61</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="I63" s="2"/>
     </row>
@@ -2241,17 +2387,17 @@
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="10" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2">
-        <v>60</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="I64" s="2"/>
     </row>
@@ -2263,10 +2409,10 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2">
-        <v>61</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="I65" s="2"/>
     </row>
@@ -2277,11 +2423,11 @@
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
-      <c r="G66" s="2">
-        <v>62</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>68</v>
+      <c r="G66" s="27">
+        <v>64</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="I66" s="2"/>
     </row>
@@ -2293,10 +2439,10 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="I67" s="2"/>
     </row>
@@ -2308,10 +2454,10 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="I68" s="2"/>
     </row>
@@ -2322,11 +2468,11 @@
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
-      <c r="G69" s="2">
-        <v>65</v>
+      <c r="G69" s="27">
+        <v>67</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="I69" s="2"/>
     </row>
@@ -2338,10 +2484,10 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="I70" s="2"/>
     </row>
@@ -2353,10 +2499,10 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="I71" s="2"/>
     </row>
@@ -2367,8 +2513,8 @@
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
-      <c r="G72" s="2">
-        <v>68</v>
+      <c r="G72" s="27">
+        <v>70</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>41</v>
@@ -2383,10 +2529,10 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="I73" s="2"/>
     </row>
@@ -2398,10 +2544,10 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I74" s="2"/>
     </row>
@@ -2412,11 +2558,11 @@
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
-      <c r="G75" s="2">
-        <v>71</v>
+      <c r="G75" s="27">
+        <v>73</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I75" s="2"/>
     </row>
@@ -2428,10 +2574,10 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="I76" s="6"/>
     </row>
@@ -2443,10 +2589,10 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="I77" s="6"/>
     </row>
@@ -2457,10 +2603,10 @@
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
-      <c r="G78" s="2">
-        <v>74</v>
-      </c>
-      <c r="H78" s="2" t="s">
+      <c r="G78" s="27">
+        <v>76</v>
+      </c>
+      <c r="H78" s="13" t="s">
         <v>41</v>
       </c>
       <c r="I78" s="2"/>
@@ -2473,10 +2619,10 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I79" s="2"/>
     </row>
@@ -2578,9 +2724,11 @@
     <hyperlink ref="B27" r:id="rId87" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{35E7190F-8175-49E0-98EF-0EC451FF7D0A}"/>
     <hyperlink ref="B28" r:id="rId88" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{1A901BFA-614C-4DED-9B55-148494546B91}"/>
     <hyperlink ref="B29" r:id="rId89" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{BCD126EB-6C4B-4A9B-A944-E10162A59054}"/>
+    <hyperlink ref="H78" r:id="rId90" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{59646BFE-4CB3-4C96-AD06-5957DCBA7535}"/>
+    <hyperlink ref="E63" r:id="rId91" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{DD82130A-554F-48DF-9317-FB3119308D6F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId90"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId92"/>
 </worksheet>
 </file>
 
@@ -2594,26 +2742,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="32"/>
-    </row>
-    <row r="2" spans="2:5" ht="28" x14ac:dyDescent="0.3">
-      <c r="B2" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>82</v>
+      <c r="B1" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>0</v>
@@ -2622,689 +2770,689 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
-        <v>0</v>
-      </c>
-      <c r="C4" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="33" t="s">
-        <v>115</v>
+      <c r="E4" s="38" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
-        <v>1</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>97</v>
+        <v>3</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>80</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="34"/>
+      <c r="E5" s="39"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>2</v>
-      </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="34"/>
+      <c r="E6" s="39"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
+        <v>5</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="24" t="s">
-        <v>3</v>
-      </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="34"/>
+      <c r="E7" s="39"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
+        <v>6</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>4</v>
-      </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="34"/>
+      <c r="E8" s="39"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
+        <v>7</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>5</v>
-      </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="34"/>
+      <c r="E9" s="39"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
+        <v>8</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="24" t="s">
-        <v>6</v>
-      </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="34"/>
+      <c r="E10" s="39"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
-        <v>7</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>98</v>
+        <v>9</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>81</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="34"/>
+      <c r="E11" s="39"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
-        <v>8</v>
-      </c>
-      <c r="C12" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="34"/>
+      <c r="E12" s="39"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
-        <v>9</v>
-      </c>
-      <c r="C13" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="34"/>
+      <c r="E13" s="39"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
-        <v>10</v>
-      </c>
-      <c r="C14" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="34"/>
+      <c r="E14" s="39"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
-        <v>11</v>
-      </c>
-      <c r="C15" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="21" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="34"/>
+      <c r="E15" s="39"/>
     </row>
     <row r="16" spans="2:5" ht="28" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E16" s="34"/>
+        <v>100</v>
+      </c>
+      <c r="E16" s="39"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
-        <v>13</v>
-      </c>
-      <c r="C17" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="34"/>
+      <c r="E17" s="39"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
-        <v>14</v>
-      </c>
-      <c r="C18" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="34"/>
+      <c r="E18" s="39"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
-        <v>15</v>
-      </c>
-      <c r="C19" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>13</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="34"/>
+      <c r="E19" s="39"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
-        <v>16</v>
-      </c>
-      <c r="C20" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="34"/>
+      <c r="E20" s="39"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
-        <v>17</v>
-      </c>
-      <c r="C21" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="34"/>
+      <c r="E21" s="39"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
-        <v>18</v>
-      </c>
-      <c r="C22" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="34"/>
+      <c r="E22" s="39"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
-        <v>19</v>
-      </c>
-      <c r="C23" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C23" s="21" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="2"/>
-      <c r="E23" s="34"/>
+      <c r="E23" s="39"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
-        <v>20</v>
-      </c>
-      <c r="C24" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="34"/>
+      <c r="E24" s="39"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
-        <v>21</v>
-      </c>
-      <c r="C25" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="21" t="s">
         <v>19</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="34"/>
+      <c r="E25" s="39"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
-        <v>22</v>
-      </c>
-      <c r="C26" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="34"/>
+      <c r="E26" s="39"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
-        <v>23</v>
-      </c>
-      <c r="C27" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="21" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="34"/>
+      <c r="E27" s="39"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
-        <v>24</v>
-      </c>
-      <c r="C28" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>22</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="34"/>
+      <c r="E28" s="39"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
-        <v>25</v>
-      </c>
-      <c r="C29" s="24" t="s">
-        <v>99</v>
+        <v>27</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="34"/>
+      <c r="E29" s="39"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
-        <v>26</v>
-      </c>
-      <c r="C30" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>23</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="34"/>
+      <c r="E30" s="39"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
-        <v>27</v>
-      </c>
-      <c r="C31" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>24</v>
       </c>
       <c r="D31" s="2"/>
-      <c r="E31" s="34"/>
+      <c r="E31" s="39"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
-        <v>28</v>
-      </c>
-      <c r="C32" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>25</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="34"/>
+      <c r="E32" s="39"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
-        <v>29</v>
-      </c>
-      <c r="C33" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>26</v>
       </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="34"/>
+      <c r="E33" s="39"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
-        <v>30</v>
-      </c>
-      <c r="C34" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>27</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="34"/>
+      <c r="E34" s="39"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
-        <v>31</v>
-      </c>
-      <c r="C35" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>28</v>
       </c>
       <c r="D35" s="2"/>
-      <c r="E35" s="34"/>
+      <c r="E35" s="39"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
-        <v>32</v>
-      </c>
-      <c r="C36" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="2"/>
-      <c r="E36" s="34"/>
+      <c r="E36" s="39"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="12">
-        <v>33</v>
-      </c>
-      <c r="C37" s="14" t="s">
+      <c r="B37" s="2">
+        <v>35</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D37" s="13"/>
-      <c r="E37" s="34"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="39"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
-        <v>34</v>
-      </c>
-      <c r="C38" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>32</v>
       </c>
       <c r="D38" s="2"/>
-      <c r="E38" s="34"/>
+      <c r="E38" s="39"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="12">
-        <v>35</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="B39" s="2">
+        <v>37</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D39" s="13"/>
-      <c r="E39" s="34"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="39"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
+        <v>38</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D40" s="2"/>
+      <c r="E40" s="39"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B41" s="2">
+        <v>39</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="34"/>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B41" s="12">
-        <v>37</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="13"/>
-      <c r="E41" s="34"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="39"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
+        <v>40</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>38</v>
-      </c>
       <c r="D42" s="2"/>
-      <c r="E42" s="34"/>
+      <c r="E42" s="39"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="12">
-        <v>39</v>
-      </c>
-      <c r="C43" s="14" t="s">
+      <c r="B43" s="2">
+        <v>41</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D43" s="13"/>
-      <c r="E43" s="34"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="39"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
-        <v>40</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" s="34"/>
+        <v>42</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E44" s="39"/>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B45" s="12">
-        <v>41</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E45" s="34"/>
+      <c r="B45" s="2">
+        <v>43</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E45" s="39"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
-        <v>42</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E46" s="34"/>
+        <v>44</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E46" s="39"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B47" s="12">
-        <v>43</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D47" s="13"/>
-      <c r="E47" s="34"/>
+      <c r="B47" s="2">
+        <v>45</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="39"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
-        <v>44</v>
-      </c>
-      <c r="C48" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="13" t="s">
         <v>42</v>
       </c>
       <c r="D48" s="2"/>
-      <c r="E48" s="34"/>
+      <c r="E48" s="39"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B49" s="12">
-        <v>45</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D49" s="13"/>
-      <c r="E49" s="34"/>
+      <c r="B49" s="2">
+        <v>47</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="12"/>
+      <c r="E49" s="39"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
+        <v>48</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="2"/>
+      <c r="E50" s="39"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51" s="2">
+        <v>49</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="12"/>
+      <c r="E51" s="39"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52" s="2">
+        <v>50</v>
+      </c>
+      <c r="C52" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="34"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B51" s="12">
+      <c r="D52" s="19"/>
+      <c r="E52" s="39"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53" s="2">
+        <v>51</v>
+      </c>
+      <c r="C53" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D51" s="13"/>
-      <c r="E51" s="34"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B52" s="20">
-        <v>48</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D52" s="21"/>
-      <c r="E52" s="34"/>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="12">
-        <v>49</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="34"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="39"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B54" s="20">
-        <v>50</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E54" s="34"/>
+      <c r="B54" s="2">
+        <v>52</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" s="39"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="12">
-        <v>51</v>
-      </c>
-      <c r="C55" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="D55" s="13"/>
-      <c r="E55" s="34"/>
+      <c r="B55" s="2">
+        <v>53</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D55" s="12"/>
+      <c r="E55" s="39"/>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="12">
-        <v>52</v>
+      <c r="B56" s="2">
+        <v>54</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D56" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E56" s="34"/>
-    </row>
-    <row r="57" spans="2:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="B57" s="20">
-        <v>53</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E57" s="34"/>
-      <c r="F57" s="27"/>
-    </row>
-    <row r="58" spans="2:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="B58" s="12">
-        <v>54</v>
+        <v>90</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="39"/>
+    </row>
+    <row r="57" spans="2:6" ht="84.5" x14ac:dyDescent="0.3">
+      <c r="B57" s="2">
+        <v>55</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D57" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="E57" s="39"/>
+      <c r="F57" s="24"/>
+    </row>
+    <row r="58" spans="2:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="B58" s="2">
+        <v>56</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="E58" s="33" t="s">
-        <v>114</v>
+        <v>72</v>
+      </c>
+      <c r="D58" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="E58" s="38" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="12">
-        <v>55</v>
+      <c r="B59" s="2">
+        <v>57</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E59" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E59" s="39"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E60" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E60" s="39"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B61" s="12">
-        <v>57</v>
+      <c r="B61" s="2">
+        <v>59</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E61" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E61" s="39"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B62" s="12">
-        <v>58</v>
+      <c r="B62" s="2">
+        <v>60</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E62" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E62" s="39"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="2">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E63" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E63" s="39"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="12">
-        <v>60</v>
+      <c r="B64" s="2">
+        <v>62</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E64" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E64" s="39"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B65" s="12">
-        <v>61</v>
+      <c r="B65" s="2">
+        <v>63</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E65" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E65" s="39"/>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>20</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E66" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E66" s="39"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B67" s="12">
-        <v>63</v>
-      </c>
-      <c r="C67" s="2" t="s">
+      <c r="B67" s="2">
+        <v>65</v>
+      </c>
+      <c r="C67" s="14" t="s">
         <v>41</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E67" s="34"/>
+        <v>75</v>
+      </c>
+      <c r="E67" s="39"/>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B68" s="12">
-        <v>64</v>
+      <c r="B68" s="2">
+        <v>66</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -3335,42 +3483,48 @@
     <hyperlink ref="C38" r:id="rId17" tooltip="所罗门 (君王)" display="https://zh.wikipedia.org/wiki/%E6%89%80%E7%BE%85%E9%96%80_(%E5%90%9B%E7%8E%8B)" xr:uid="{03B51CEB-C5A0-4737-BD85-A80A5286B1D3}"/>
     <hyperlink ref="C37" r:id="rId18" tooltip="大卫王" display="https://zh.wikipedia.org/wiki/%E5%A4%A7%E8%A1%9B%E7%8E%8B" xr:uid="{80E557AD-A19A-47D5-A69C-8530541A76A5}"/>
     <hyperlink ref="C57" r:id="rId19" xr:uid="{19DA0B9C-C79B-4D73-BD61-2298F262C554}"/>
-    <hyperlink ref="D58" r:id="rId20" location="%E6%89%80%E7%BD%97%E5%B7%B4%E4%BC%AF%E7%9A%84%E5%84%BF%E5%AD%90" display="耶稣的谱系#所罗巴伯的儿子" xr:uid="{F028C71B-26F9-4042-8715-2FA152B6077D}"/>
-    <hyperlink ref="C4" r:id="rId21" tooltip="亚当" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E7%95%B6" xr:uid="{D91F2ECA-8206-403D-BF1E-7A61A39AFC4C}"/>
-    <hyperlink ref="C5" r:id="rId22" tooltip="塞特" display="https://zh.wikipedia.org/wiki/%E5%A1%9E%E7%89%B9" xr:uid="{5682E5C8-9E0E-40CB-A11C-3E04AC1932F3}"/>
-    <hyperlink ref="C6" r:id="rId23" tooltip="以挪士" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%8C%AA%E5%A3%AB" xr:uid="{3D22BE58-C482-4F3D-A9FD-4C4F20470042}"/>
-    <hyperlink ref="C7" r:id="rId24" tooltip="该南" display="https://zh.wikipedia.org/wiki/%E8%AF%A5%E5%8D%97" xr:uid="{E377CA79-2D58-4054-AA8A-DBF1DFF6158D}"/>
-    <hyperlink ref="C8" r:id="rId25" tooltip="玛勒列" display="https://zh.wikipedia.org/wiki/%E7%8E%9B%E5%8B%92%E5%88%97" xr:uid="{19B5A2E1-A408-4520-B90D-F47F15AFDCB1}"/>
-    <hyperlink ref="C9" r:id="rId26" tooltip="雅列" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%88%97" xr:uid="{0459124F-099A-4E92-BE69-CE31019D9B36}"/>
-    <hyperlink ref="C10" r:id="rId27" tooltip="以诺" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E8%AB%BE" xr:uid="{6C8CC7C4-F011-4299-9BD7-BA50DB9DB7A3}"/>
-    <hyperlink ref="C11" r:id="rId28" tooltip="玛土撒拉" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E5%9C%9F%E6%92%92%E6%8B%89" xr:uid="{84AEF96F-9442-460C-9537-D3FF5E138875}"/>
-    <hyperlink ref="C12" r:id="rId29" tooltip="拉麦" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E9%BA%A6" xr:uid="{A8DB2E60-2205-4612-A7B2-CB8693E28AA3}"/>
-    <hyperlink ref="C13" r:id="rId30" tooltip="挪亚" display="https://zh.wikipedia.org/wiki/%E6%8C%AA%E4%BA%9E" xr:uid="{9A10F4C0-14D5-4273-B40E-04B4BB16C1ED}"/>
-    <hyperlink ref="C14" r:id="rId31" tooltip="闪 (圣经)" display="https://zh.wikipedia.org/wiki/%E9%96%83_(%E8%81%96%E7%B6%93)" xr:uid="{B5F37A7D-8280-4A5E-B393-85A2E0CBFA89}"/>
-    <hyperlink ref="C15" r:id="rId32" tooltip="亚法撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E6%B3%95%E6%92%92" xr:uid="{9487E042-5D95-4BD1-8265-C1F67B23BB26}"/>
-    <hyperlink ref="C17" r:id="rId33" tooltip="沙拉 (圣经人物)" display="https://zh.wikipedia.org/wiki/%E6%B2%99%E6%8B%89_(%E5%9C%A3%E7%BB%8F%E4%BA%BA%E7%89%A9)" xr:uid="{70420CCF-87F7-4476-8446-2FBE69CFFB70}"/>
-    <hyperlink ref="C18" r:id="rId34" tooltip="希伯" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E4%BC%AF" xr:uid="{D6E27536-AE40-4A01-B2C0-EECAE77AA236}"/>
-    <hyperlink ref="C19" r:id="rId35" tooltip="法勒" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92" xr:uid="{9E7DE66B-3310-4766-8CF2-8A4700F92548}"/>
-    <hyperlink ref="C20" r:id="rId36" tooltip="拉吴" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E5%90%B4" xr:uid="{C4BC748A-4E43-4D88-8F45-3FF656DEDB70}"/>
-    <hyperlink ref="C21" r:id="rId37" tooltip="西鹿" display="https://zh.wikipedia.org/wiki/%E8%A5%BF%E9%B9%BF" xr:uid="{CD8C3835-2AC2-4D27-85DB-966FD3099464}"/>
-    <hyperlink ref="C22" r:id="rId38" tooltip="拿鹤" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%B9%A4" xr:uid="{63896651-57FE-4A10-A6FC-8877CFE2164B}"/>
-    <hyperlink ref="C23" r:id="rId39" tooltip="他拉" display="https://zh.wikipedia.org/wiki/%E4%BB%96%E6%8B%89" xr:uid="{D6088842-3C2D-401D-BA00-C30393CE0B21}"/>
-    <hyperlink ref="C24" r:id="rId40" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{4B892FC3-E34E-4ABF-BF9B-0986AA274D46}"/>
-    <hyperlink ref="C25" r:id="rId41" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{A9307EC9-C8C9-47ED-8219-7E3502B90F63}"/>
-    <hyperlink ref="C26" r:id="rId42" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{6A338BA4-EF55-4C71-AF27-7A5FBA074037}"/>
-    <hyperlink ref="C27" r:id="rId43" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{C6E79DDC-2A91-4A93-A384-2103381567D2}"/>
-    <hyperlink ref="C28" r:id="rId44" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{626B9A97-7547-420D-8C2A-1171F9746C8A}"/>
-    <hyperlink ref="C29" r:id="rId45" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{6FF395F4-4DD7-44FA-8809-496908535532}"/>
-    <hyperlink ref="C30" r:id="rId46" tooltip="亚兰" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E5%85%B0" xr:uid="{BFC871F3-C41F-4237-A422-066E1C6E8752}"/>
-    <hyperlink ref="C31" r:id="rId47" tooltip="亚米拿达" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E7%B1%B3%E6%8B%BF%E8%BE%BE" xr:uid="{DC54AF48-ABFF-436D-A79E-629582C19C8C}"/>
-    <hyperlink ref="C32" r:id="rId48" tooltip="拿顺" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%A1%BA" xr:uid="{6405FB9D-B96F-42ED-B1E0-5C7853932202}"/>
-    <hyperlink ref="C33" r:id="rId49" tooltip="撒门" display="https://zh.wikipedia.org/wiki/%E6%92%92%E9%97%A8" xr:uid="{C0E9A834-9566-4216-819F-14B61E7295BB}"/>
-    <hyperlink ref="C34" r:id="rId50" tooltip="波阿斯" display="https://zh.wikipedia.org/wiki/%E6%B3%A2%E9%98%BF%E6%96%AF" xr:uid="{91DB3C24-C842-44D0-B7A0-2B2FDC9AB3C1}"/>
-    <hyperlink ref="C35" r:id="rId51" tooltip="俄备得" display="https://zh.wikipedia.org/wiki/%E4%BF%84%E5%A4%87%E5%BE%97" xr:uid="{8234E72B-B474-4A3E-8B85-C04621638E2A}"/>
-    <hyperlink ref="C36" r:id="rId52" tooltip="耶西" display="https://zh.wikipedia.org/wiki/%E8%80%B6%E8%A5%BF" xr:uid="{11C68BAE-BF57-4E50-8EA2-F58C7EF02CC3}"/>
-    <hyperlink ref="C55" r:id="rId53" xr:uid="{1CC4AE70-C96A-4663-991A-C6C3C061D194}"/>
+    <hyperlink ref="C4" r:id="rId20" tooltip="亚当" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E7%95%B6" xr:uid="{D91F2ECA-8206-403D-BF1E-7A61A39AFC4C}"/>
+    <hyperlink ref="C5" r:id="rId21" tooltip="塞特" display="https://zh.wikipedia.org/wiki/%E5%A1%9E%E7%89%B9" xr:uid="{5682E5C8-9E0E-40CB-A11C-3E04AC1932F3}"/>
+    <hyperlink ref="C6" r:id="rId22" tooltip="以挪士" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%8C%AA%E5%A3%AB" xr:uid="{3D22BE58-C482-4F3D-A9FD-4C4F20470042}"/>
+    <hyperlink ref="C7" r:id="rId23" tooltip="该南" display="https://zh.wikipedia.org/wiki/%E8%AF%A5%E5%8D%97" xr:uid="{E377CA79-2D58-4054-AA8A-DBF1DFF6158D}"/>
+    <hyperlink ref="C8" r:id="rId24" tooltip="玛勒列" display="https://zh.wikipedia.org/wiki/%E7%8E%9B%E5%8B%92%E5%88%97" xr:uid="{19B5A2E1-A408-4520-B90D-F47F15AFDCB1}"/>
+    <hyperlink ref="C9" r:id="rId25" tooltip="雅列" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%88%97" xr:uid="{0459124F-099A-4E92-BE69-CE31019D9B36}"/>
+    <hyperlink ref="C10" r:id="rId26" tooltip="以诺" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E8%AB%BE" xr:uid="{6C8CC7C4-F011-4299-9BD7-BA50DB9DB7A3}"/>
+    <hyperlink ref="C11" r:id="rId27" tooltip="玛土撒拉" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E5%9C%9F%E6%92%92%E6%8B%89" xr:uid="{84AEF96F-9442-460C-9537-D3FF5E138875}"/>
+    <hyperlink ref="C12" r:id="rId28" tooltip="拉麦" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E9%BA%A6" xr:uid="{A8DB2E60-2205-4612-A7B2-CB8693E28AA3}"/>
+    <hyperlink ref="C13" r:id="rId29" tooltip="挪亚" display="https://zh.wikipedia.org/wiki/%E6%8C%AA%E4%BA%9E" xr:uid="{9A10F4C0-14D5-4273-B40E-04B4BB16C1ED}"/>
+    <hyperlink ref="C14" r:id="rId30" tooltip="闪 (圣经)" display="https://zh.wikipedia.org/wiki/%E9%96%83_(%E8%81%96%E7%B6%93)" xr:uid="{B5F37A7D-8280-4A5E-B393-85A2E0CBFA89}"/>
+    <hyperlink ref="C15" r:id="rId31" tooltip="亚法撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E6%B3%95%E6%92%92" xr:uid="{9487E042-5D95-4BD1-8265-C1F67B23BB26}"/>
+    <hyperlink ref="C17" r:id="rId32" tooltip="沙拉 (圣经人物)" display="https://zh.wikipedia.org/wiki/%E6%B2%99%E6%8B%89_(%E5%9C%A3%E7%BB%8F%E4%BA%BA%E7%89%A9)" xr:uid="{70420CCF-87F7-4476-8446-2FBE69CFFB70}"/>
+    <hyperlink ref="C18" r:id="rId33" tooltip="希伯" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E4%BC%AF" xr:uid="{D6E27536-AE40-4A01-B2C0-EECAE77AA236}"/>
+    <hyperlink ref="C19" r:id="rId34" tooltip="法勒" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92" xr:uid="{9E7DE66B-3310-4766-8CF2-8A4700F92548}"/>
+    <hyperlink ref="C20" r:id="rId35" tooltip="拉吴" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E5%90%B4" xr:uid="{C4BC748A-4E43-4D88-8F45-3FF656DEDB70}"/>
+    <hyperlink ref="C21" r:id="rId36" tooltip="西鹿" display="https://zh.wikipedia.org/wiki/%E8%A5%BF%E9%B9%BF" xr:uid="{CD8C3835-2AC2-4D27-85DB-966FD3099464}"/>
+    <hyperlink ref="C22" r:id="rId37" tooltip="拿鹤" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%B9%A4" xr:uid="{63896651-57FE-4A10-A6FC-8877CFE2164B}"/>
+    <hyperlink ref="C23" r:id="rId38" tooltip="他拉" display="https://zh.wikipedia.org/wiki/%E4%BB%96%E6%8B%89" xr:uid="{D6088842-3C2D-401D-BA00-C30393CE0B21}"/>
+    <hyperlink ref="C24" r:id="rId39" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{4B892FC3-E34E-4ABF-BF9B-0986AA274D46}"/>
+    <hyperlink ref="C25" r:id="rId40" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{A9307EC9-C8C9-47ED-8219-7E3502B90F63}"/>
+    <hyperlink ref="C26" r:id="rId41" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{6A338BA4-EF55-4C71-AF27-7A5FBA074037}"/>
+    <hyperlink ref="C27" r:id="rId42" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{C6E79DDC-2A91-4A93-A384-2103381567D2}"/>
+    <hyperlink ref="C28" r:id="rId43" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{626B9A97-7547-420D-8C2A-1171F9746C8A}"/>
+    <hyperlink ref="C29" r:id="rId44" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{6FF395F4-4DD7-44FA-8809-496908535532}"/>
+    <hyperlink ref="C30" r:id="rId45" tooltip="亚兰" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E5%85%B0" xr:uid="{BFC871F3-C41F-4237-A422-066E1C6E8752}"/>
+    <hyperlink ref="C31" r:id="rId46" tooltip="亚米拿达" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E7%B1%B3%E6%8B%BF%E8%BE%BE" xr:uid="{DC54AF48-ABFF-436D-A79E-629582C19C8C}"/>
+    <hyperlink ref="C32" r:id="rId47" tooltip="拿顺" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%A1%BA" xr:uid="{6405FB9D-B96F-42ED-B1E0-5C7853932202}"/>
+    <hyperlink ref="C33" r:id="rId48" tooltip="撒门" display="https://zh.wikipedia.org/wiki/%E6%92%92%E9%97%A8" xr:uid="{C0E9A834-9566-4216-819F-14B61E7295BB}"/>
+    <hyperlink ref="C34" r:id="rId49" tooltip="波阿斯" display="https://zh.wikipedia.org/wiki/%E6%B3%A2%E9%98%BF%E6%96%AF" xr:uid="{91DB3C24-C842-44D0-B7A0-2B2FDC9AB3C1}"/>
+    <hyperlink ref="C35" r:id="rId50" tooltip="俄备得" display="https://zh.wikipedia.org/wiki/%E4%BF%84%E5%A4%87%E5%BE%97" xr:uid="{8234E72B-B474-4A3E-8B85-C04621638E2A}"/>
+    <hyperlink ref="C36" r:id="rId51" tooltip="耶西" display="https://zh.wikipedia.org/wiki/%E8%80%B6%E8%A5%BF" xr:uid="{11C68BAE-BF57-4E50-8EA2-F58C7EF02CC3}"/>
+    <hyperlink ref="C55" r:id="rId52" xr:uid="{1CC4AE70-C96A-4663-991A-C6C3C061D194}"/>
+    <hyperlink ref="D44" r:id="rId53" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{A357BE76-24D8-471A-B7BA-68629EFBACE2}"/>
+    <hyperlink ref="D45" r:id="rId54" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{47696524-5AD8-4A07-B660-AF10253EBFFF}"/>
+    <hyperlink ref="D46" r:id="rId55" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{971C962A-47BF-4EFF-AD02-EDEB2659F862}"/>
+    <hyperlink ref="D54" r:id="rId56" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约西亚生耶哥尼雅" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{79E51E53-FF4B-4187-8EE9-8A103052F237}"/>
+    <hyperlink ref="D56" r:id="rId57" location="%E7%AC%AC%E4%B8%89%E7%AB%A0" tooltip="耶哥尼雅被掳．他的儿子是撒拉铁、毘大雅......毘大雅的儿子是所罗巴伯......" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E5%8E%86%E4%BB%A3%E5%BF%97%E4%B8%8A - %E7%AC%AC%E4%B8%89%E7%AB%A0" xr:uid="{47116252-6F27-41AD-B956-8479A01C4E8D}"/>
+    <hyperlink ref="C67" r:id="rId58" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{1ECBF5AF-1065-423E-9ADD-3EE804376680}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId59"/>
 </worksheet>
 </file>
 

--- a/其它格式未转换/耶稣家谱/耶稣家谱.xlsx
+++ b/其它格式未转换/耶稣家谱/耶稣家谱.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文件\notes\其它格式未转换\耶稣家谱\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AEF5734-8F00-44BD-A5EC-AAB2C0670690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A24A2A3D-15F9-4CA4-9D34-CC1AB4683CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -344,11 +344,6 @@
   </si>
   <si>
     <t>亚法撒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>《旧约》（创10:24）（历上1:18）引用的是希伯来原文，没有该南。
-《新约》（路加3:36）引用的是希腊文《七十士译本》，包含该南。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -561,6 +556,10 @@
     <t>代数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -594,6 +593,7 @@
       <sz val="11"/>
       <color theme="10"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -765,7 +765,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -850,12 +850,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -885,12 +888,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1182,28 +1179,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="42.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="31" t="s">
+      <c r="A1" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="30" t="s">
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="28" t="s">
         <v>65</v>
       </c>
       <c r="D2" s="8" t="s">
@@ -1216,7 +1215,7 @@
         <v>65</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H2" s="7" t="s">
         <v>61</v>
@@ -1226,8 +1225,12 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="A3" s="27">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="27"/>
       <c r="E3" s="27"/>
@@ -1241,7 +1244,9 @@
       <c r="I3" s="27"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
       <c r="B4" s="21" t="s">
         <v>1</v>
       </c>
@@ -1258,7 +1263,9 @@
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
       <c r="B5" s="21" t="s">
         <v>80</v>
       </c>
@@ -1275,7 +1282,9 @@
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
+      <c r="A6" s="27">
+        <v>4</v>
+      </c>
       <c r="B6" s="21" t="s">
         <v>2</v>
       </c>
@@ -1292,7 +1301,9 @@
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
       <c r="B7" s="21" t="s">
         <v>3</v>
       </c>
@@ -1309,7 +1320,9 @@
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
       <c r="B8" s="21" t="s">
         <v>4</v>
       </c>
@@ -1326,7 +1339,9 @@
       <c r="I8" s="2"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
+      <c r="A9" s="27">
+        <v>7</v>
+      </c>
       <c r="B9" s="21" t="s">
         <v>5</v>
       </c>
@@ -1343,7 +1358,9 @@
       <c r="I9" s="2"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
       <c r="B10" s="21" t="s">
         <v>6</v>
       </c>
@@ -1360,7 +1377,9 @@
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
       <c r="B11" s="21" t="s">
         <v>81</v>
       </c>
@@ -1377,7 +1396,9 @@
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
+      <c r="A12" s="27">
+        <v>10</v>
+      </c>
       <c r="B12" s="21" t="s">
         <v>7</v>
       </c>
@@ -1394,7 +1415,9 @@
       <c r="I12" s="2"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
       <c r="B13" s="21" t="s">
         <v>8</v>
       </c>
@@ -1411,7 +1434,9 @@
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
       <c r="B14" s="21" t="s">
         <v>9</v>
       </c>
@@ -1428,7 +1453,9 @@
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
+      <c r="A15" s="27">
+        <v>13</v>
+      </c>
       <c r="B15" s="17" t="s">
         <v>95</v>
       </c>
@@ -1445,12 +1472,14 @@
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" ht="56" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>11</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -1462,13 +1491,15 @@
         <v>3</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
       <c r="B17" s="21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -1483,9 +1514,11 @@
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
+      <c r="A18" s="27">
+        <v>16</v>
+      </c>
       <c r="B18" s="21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1500,9 +1533,11 @@
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
       <c r="B19" s="21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -1517,9 +1552,11 @@
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
       <c r="B20" s="21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -1534,9 +1571,11 @@
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
+      <c r="A21" s="27">
+        <v>19</v>
+      </c>
       <c r="B21" s="21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -1551,9 +1590,11 @@
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
       <c r="B22" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1568,9 +1609,11 @@
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
       <c r="B23" s="21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -1585,9 +1628,11 @@
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
+      <c r="A24" s="27">
+        <v>22</v>
+      </c>
       <c r="B24" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="11">
@@ -1606,9 +1651,11 @@
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
       <c r="B25" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="11">
@@ -1627,9 +1674,11 @@
       <c r="I25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
       <c r="B26" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="11">
@@ -1648,9 +1697,11 @@
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
+      <c r="A27" s="27">
+        <v>25</v>
+      </c>
       <c r="B27" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="11">
@@ -1669,9 +1720,11 @@
       <c r="I27" s="2"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
       <c r="B28" s="21" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="11">
@@ -1691,9 +1744,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2"/>
-      <c r="B29" s="21" t="s">
-        <v>82</v>
-      </c>
+      <c r="B29" s="21"/>
       <c r="C29" s="2"/>
       <c r="D29" s="11">
         <v>6</v>
@@ -1858,7 +1909,7 @@
         <v>35</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I37" s="4"/>
     </row>
@@ -1987,7 +2038,7 @@
         <v>87</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G44" s="2">
         <v>42</v>
@@ -2012,7 +2063,7 @@
         <v>43</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I45" s="2"/>
     </row>
@@ -2031,7 +2082,7 @@
         <v>44</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I46" s="2"/>
     </row>
@@ -2050,7 +2101,7 @@
         <v>45</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I47" s="2"/>
     </row>
@@ -2088,7 +2139,7 @@
         <v>47</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I49" s="2"/>
     </row>
@@ -2107,7 +2158,7 @@
         <v>48</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I50" s="2"/>
     </row>
@@ -2128,7 +2179,7 @@
         <v>49</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I51" s="2"/>
     </row>
@@ -2147,7 +2198,7 @@
         <v>50</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I52" s="2"/>
     </row>
@@ -2168,7 +2219,7 @@
         <v>51</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I53" s="2"/>
     </row>
@@ -2189,7 +2240,7 @@
         <v>52</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I54" s="2"/>
     </row>
@@ -2210,7 +2261,7 @@
         <v>53</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I55" s="2"/>
     </row>
@@ -2231,7 +2282,7 @@
         <v>54</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I56" s="2"/>
     </row>
@@ -2252,7 +2303,7 @@
         <v>55</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I57" s="2"/>
     </row>
@@ -2315,7 +2366,7 @@
         <v>58</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I60" s="2"/>
     </row>
@@ -2336,7 +2387,7 @@
         <v>59</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I61" s="2"/>
     </row>
@@ -2357,7 +2408,7 @@
         <v>60</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I62" s="2"/>
     </row>
@@ -2378,7 +2429,7 @@
         <v>61</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I63" s="2"/>
     </row>
@@ -2397,7 +2448,7 @@
         <v>62</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I64" s="2"/>
     </row>
@@ -2412,7 +2463,7 @@
         <v>63</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I65" s="2"/>
     </row>
@@ -2427,7 +2478,7 @@
         <v>64</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I66" s="2"/>
     </row>
@@ -2711,30 +2762,20 @@
     <hyperlink ref="B13" r:id="rId74" tooltip="挪亚" display="https://zh.wikipedia.org/wiki/%E6%8C%AA%E4%BA%9E" xr:uid="{90CBFDA1-CED2-4431-AAD2-6089017A8F63}"/>
     <hyperlink ref="B14" r:id="rId75" tooltip="闪 (圣经)" display="https://zh.wikipedia.org/wiki/%E9%96%83_(%E8%81%96%E7%B6%93)" xr:uid="{CCC9280C-5E78-4AE7-BDDB-9BD2710E2AF7}"/>
     <hyperlink ref="B15" r:id="rId76" tooltip="亚法撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E6%B3%95%E6%92%92" xr:uid="{C8E15ADE-B5B5-4881-BFD9-6EE0231D17D6}"/>
-    <hyperlink ref="B17" r:id="rId77" tooltip="沙拉 (圣经人物)" display="https://zh.wikipedia.org/wiki/%E6%B2%99%E6%8B%89_(%E5%9C%A3%E7%BB%8F%E4%BA%BA%E7%89%A9)" xr:uid="{F623895D-8BC1-4E53-843E-9E375E2F4A99}"/>
-    <hyperlink ref="B18" r:id="rId78" tooltip="希伯" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E4%BC%AF" xr:uid="{0BB9151E-7A8D-4423-9A84-FB8F03985037}"/>
-    <hyperlink ref="B19" r:id="rId79" tooltip="法勒" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92" xr:uid="{3551A306-AA2F-4CEE-A062-3B4BBBD117FD}"/>
-    <hyperlink ref="B20" r:id="rId80" tooltip="拉吴" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E5%90%B4" xr:uid="{64ECE156-E51F-4204-9A1E-B69F41ECE150}"/>
-    <hyperlink ref="B21" r:id="rId81" tooltip="西鹿" display="https://zh.wikipedia.org/wiki/%E8%A5%BF%E9%B9%BF" xr:uid="{421F4ADD-DB7C-4DB8-933B-CFC005303684}"/>
-    <hyperlink ref="B22" r:id="rId82" tooltip="拿鹤" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%B9%A4" xr:uid="{3A6A833E-6CCA-426D-BACB-EFC7CEDC0C5F}"/>
-    <hyperlink ref="B23" r:id="rId83" tooltip="他拉" display="https://zh.wikipedia.org/wiki/%E4%BB%96%E6%8B%89" xr:uid="{980EFDAD-81E6-4F88-8487-32337CD055B1}"/>
-    <hyperlink ref="B24" r:id="rId84" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{73264DE7-3452-45F3-B152-873A1C4D6B78}"/>
-    <hyperlink ref="B25" r:id="rId85" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{ACFB9A22-6CEB-4FAA-82A2-149FC3A7411B}"/>
-    <hyperlink ref="B26" r:id="rId86" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{D4098122-6EB7-4374-895F-3878995D434F}"/>
-    <hyperlink ref="B27" r:id="rId87" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{35E7190F-8175-49E0-98EF-0EC451FF7D0A}"/>
-    <hyperlink ref="B28" r:id="rId88" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{1A901BFA-614C-4DED-9B55-148494546B91}"/>
-    <hyperlink ref="B29" r:id="rId89" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{BCD126EB-6C4B-4A9B-A944-E10162A59054}"/>
-    <hyperlink ref="H78" r:id="rId90" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{59646BFE-4CB3-4C96-AD06-5957DCBA7535}"/>
-    <hyperlink ref="E63" r:id="rId91" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{DD82130A-554F-48DF-9317-FB3119308D6F}"/>
+    <hyperlink ref="H78" r:id="rId77" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{59646BFE-4CB3-4C96-AD06-5957DCBA7535}"/>
+    <hyperlink ref="E63" r:id="rId78" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{DD82130A-554F-48DF-9317-FB3119308D6F}"/>
+    <hyperlink ref="B16" r:id="rId79" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{1C69E6B0-8E9A-4CEB-864A-033BCCD5795D}"/>
+    <hyperlink ref="B17" r:id="rId80" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{D0157683-A459-487A-ADCF-EDCBE0F67677}"/>
+    <hyperlink ref="B18" r:id="rId81" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{5E5880D9-4E0A-4C8F-8801-32FE961DC216}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId92"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId82"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0009E5F3-39F5-4B5B-8B2C-16350CEAF2FD}">
-  <dimension ref="B1:F68"/>
+  <dimension ref="B1:F67"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="18.25" style="1" bestFit="1" customWidth="1"/>
@@ -2742,15 +2783,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="38"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>61</v>
@@ -2776,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="2"/>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="39" t="s">
         <v>93</v>
       </c>
     </row>
@@ -2788,7 +2829,7 @@
         <v>80</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="39"/>
+      <c r="E5" s="40"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -2798,7 +2839,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="39"/>
+      <c r="E6" s="40"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -2808,7 +2849,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="2"/>
-      <c r="E7" s="39"/>
+      <c r="E7" s="40"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -2818,7 +2859,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="2"/>
-      <c r="E8" s="39"/>
+      <c r="E8" s="40"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
@@ -2828,7 +2869,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="2"/>
-      <c r="E9" s="39"/>
+      <c r="E9" s="40"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
@@ -2838,7 +2879,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="39"/>
+      <c r="E10" s="40"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
@@ -2848,7 +2889,7 @@
         <v>81</v>
       </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="39"/>
+      <c r="E11" s="40"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
@@ -2858,7 +2899,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="2"/>
-      <c r="E12" s="39"/>
+      <c r="E12" s="40"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
@@ -2868,7 +2909,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2"/>
-      <c r="E13" s="39"/>
+      <c r="E13" s="40"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
@@ -2878,7 +2919,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="39"/>
+      <c r="E14" s="40"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
@@ -2888,601 +2929,591 @@
         <v>10</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="E15" s="39"/>
+      <c r="E15" s="40"/>
     </row>
     <row r="16" spans="2:5" ht="28" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>14</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>3</v>
+      <c r="C16" s="21" t="s">
+        <v>11</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" s="39"/>
+        <v>99</v>
+      </c>
+      <c r="E16" s="40"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>15</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="39"/>
+      <c r="E17" s="40"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>16</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2"/>
-      <c r="E18" s="39"/>
+      <c r="E18" s="40"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>17</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="39"/>
+      <c r="E19" s="40"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>18</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D20" s="2"/>
-      <c r="E20" s="39"/>
+      <c r="E20" s="40"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>19</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" s="2"/>
-      <c r="E21" s="39"/>
+      <c r="E21" s="40"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>20</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D22" s="2"/>
-      <c r="E22" s="39"/>
+      <c r="E22" s="40"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>21</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="39"/>
+        <v>18</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="40"/>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>22</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="39"/>
+        <v>19</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="40"/>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>23</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="39"/>
+      <c r="E25" s="40"/>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>24</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D26" s="2"/>
-      <c r="E26" s="39"/>
+      <c r="E26" s="40"/>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>25</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="39"/>
+      <c r="E27" s="40"/>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>26</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="D28" s="2"/>
-      <c r="E28" s="39"/>
+      <c r="E28" s="40"/>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>27</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="39"/>
+      <c r="E29" s="40"/>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>28</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D30" s="2"/>
-      <c r="E30" s="39"/>
+      <c r="E30" s="40"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>29</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31" s="2"/>
-      <c r="E31" s="39"/>
+      <c r="E31" s="40"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>30</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="39"/>
+      <c r="E32" s="40"/>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>31</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D33" s="2"/>
-      <c r="E33" s="39"/>
+      <c r="E33" s="40"/>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <v>32</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34" s="2"/>
-      <c r="E34" s="39"/>
+      <c r="E34" s="40"/>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <v>33</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D35" s="2"/>
-      <c r="E35" s="39"/>
+      <c r="E35" s="40"/>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <v>34</v>
       </c>
-      <c r="C36" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="2"/>
-      <c r="E36" s="39"/>
+      <c r="C36" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D36" s="12"/>
+      <c r="E36" s="40"/>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>35</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="12"/>
-      <c r="E37" s="39"/>
+        <v>32</v>
+      </c>
+      <c r="D37" s="2"/>
+      <c r="E37" s="40"/>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <v>36</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="2"/>
-      <c r="E38" s="39"/>
+        <v>33</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="40"/>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <v>37</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D39" s="12"/>
-      <c r="E39" s="39"/>
+      <c r="C39" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D39" s="2"/>
+      <c r="E39" s="40"/>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <v>38</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="39"/>
+      <c r="C40" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="40"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <v>39</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D41" s="12"/>
-      <c r="E41" s="39"/>
+        <v>38</v>
+      </c>
+      <c r="D41" s="2"/>
+      <c r="E41" s="40"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <v>40</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="39"/>
+        <v>40</v>
+      </c>
+      <c r="D42" s="12"/>
+      <c r="E42" s="40"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <v>41</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D43" s="12"/>
-      <c r="E43" s="39"/>
+      <c r="C43" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="40"/>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>42</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>58</v>
+      <c r="C44" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E44" s="39"/>
+        <v>118</v>
+      </c>
+      <c r="E44" s="40"/>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <v>43</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E45" s="39"/>
+        <v>118</v>
+      </c>
+      <c r="E45" s="40"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>44</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D46" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="E46" s="39"/>
+        <v>87</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="40"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>45</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="39"/>
+        <v>42</v>
+      </c>
+      <c r="D47" s="2"/>
+      <c r="E47" s="40"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>46</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="39"/>
+        <v>43</v>
+      </c>
+      <c r="D48" s="12"/>
+      <c r="E48" s="40"/>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>47</v>
       </c>
-      <c r="C49" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D49" s="12"/>
-      <c r="E49" s="39"/>
+      <c r="C49" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D49" s="2"/>
+      <c r="E49" s="40"/>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>48</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="39"/>
+      <c r="C50" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D50" s="12"/>
+      <c r="E50" s="40"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <v>49</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="12"/>
-      <c r="E51" s="39"/>
+        <v>46</v>
+      </c>
+      <c r="D51" s="19"/>
+      <c r="E51" s="40"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <v>50</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D52" s="19"/>
-      <c r="E52" s="39"/>
+        <v>47</v>
+      </c>
+      <c r="D52" s="12"/>
+      <c r="E52" s="40"/>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <v>51</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53" s="12"/>
-      <c r="E53" s="39"/>
+        <v>68</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53" s="40"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <v>52</v>
       </c>
-      <c r="C54" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D54" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E54" s="39"/>
+      <c r="C54" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D54" s="12"/>
+      <c r="E54" s="40"/>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <v>53</v>
       </c>
-      <c r="C55" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D55" s="12"/>
-      <c r="E55" s="39"/>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C55" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55" s="40"/>
+    </row>
+    <row r="56" spans="2:6" ht="84.5" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <v>54</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" s="13" t="s">
+      <c r="C56" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="E56" s="39"/>
-    </row>
-    <row r="57" spans="2:6" ht="84.5" x14ac:dyDescent="0.3">
+      <c r="E56" s="40"/>
+      <c r="F56" s="24"/>
+    </row>
+    <row r="57" spans="2:6" ht="42" x14ac:dyDescent="0.3">
       <c r="B57" s="2">
         <v>55</v>
       </c>
-      <c r="C57" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D57" s="40" t="s">
+      <c r="C57" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="E57" s="39"/>
-      <c r="F57" s="24"/>
-    </row>
-    <row r="58" spans="2:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="E57" s="39" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B58" s="2">
         <v>56</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D58" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E58" s="38" t="s">
-        <v>92</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E58" s="40"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B59" s="2">
         <v>57</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E59" s="39"/>
+      <c r="E59" s="40"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
         <v>58</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E60" s="39"/>
+      <c r="E60" s="40"/>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B61" s="2">
         <v>59</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E61" s="39"/>
+      <c r="E61" s="40"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B62" s="2">
         <v>60</v>
       </c>
-      <c r="C62" s="6" t="s">
-        <v>78</v>
+      <c r="C62" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E62" s="39"/>
+      <c r="E62" s="40"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B63" s="2">
         <v>61</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>49</v>
+      <c r="C63" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E63" s="39"/>
+      <c r="E63" s="40"/>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
         <v>62</v>
       </c>
-      <c r="C64" s="6" t="s">
-        <v>79</v>
+      <c r="C64" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E64" s="39"/>
+      <c r="E64" s="40"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65" s="2">
         <v>63</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E65" s="39"/>
+      <c r="E65" s="40"/>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66" s="2">
         <v>64</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>20</v>
+      <c r="C66" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="E66" s="39"/>
+      <c r="E66" s="40"/>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67" s="2">
         <v>65</v>
       </c>
-      <c r="C67" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E67" s="39"/>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B68" s="2">
-        <v>66</v>
-      </c>
-      <c r="C68" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D68" s="2"/>
+      <c r="D67" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E58:E67"/>
-    <mergeCell ref="E4:E57"/>
+    <mergeCell ref="E57:E66"/>
+    <mergeCell ref="E4:E56"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C54" r:id="rId1" tooltip="约雅敬" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E9%9B%85%E6%95%AC" xr:uid="{439A29C8-3C48-4332-A148-A1FE722B0B58}"/>
-    <hyperlink ref="C53" r:id="rId2" tooltip="约西亚" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E8%A5%BF%E4%BA%9E" xr:uid="{ECD3B9E9-B98F-4547-9106-7559A825DAD2}"/>
-    <hyperlink ref="C52" r:id="rId3" tooltip="亚们" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%80%91" xr:uid="{8732A9A7-D22A-495B-AC2C-00D8B92F93D9}"/>
-    <hyperlink ref="C51" r:id="rId4" tooltip="玛拿西 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E6%8B%BF%E8%A5%BF_(%E7%8C%B6%E5%A4%A7)" xr:uid="{3E6DBFCD-8A02-4D0A-97C9-9995E8C33208}"/>
-    <hyperlink ref="C50" r:id="rId5" tooltip="希西家" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E8%A5%BF%E5%AE%B6" xr:uid="{928A15B1-E352-48C2-B27F-F11E91FA7EA6}"/>
-    <hyperlink ref="C49" r:id="rId6" tooltip="亚哈斯" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%93%88%E6%96%AF" xr:uid="{0DC09F59-2904-4FBD-A9B8-FFDD9499A09E}"/>
-    <hyperlink ref="C48" r:id="rId7" tooltip="约坦" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E5%9D%A6" xr:uid="{6DE869B8-8245-4894-A5E3-E7B745007249}"/>
-    <hyperlink ref="C47" r:id="rId8" tooltip="乌西雅" xr:uid="{79334C27-6158-4B0E-B22D-93C5F10D9F42}"/>
-    <hyperlink ref="C46" r:id="rId9" tooltip="亚玛谢" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E7%91%AA%E8%AC%9D" xr:uid="{4E70B4E6-A86A-4406-B435-9CD8D5E6A131}"/>
-    <hyperlink ref="C45" r:id="rId10" tooltip="约阿施 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E9%98%BF%E6%96%BD_(%E7%8C%B6%E5%A4%A7)" xr:uid="{C59FD51A-5399-4F71-AA04-5C8794B167E1}"/>
-    <hyperlink ref="C44" r:id="rId11" tooltip="亚哈谢 (犹大)" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%93%88%E8%AC%9D_(%E7%8C%B6%E5%A4%A7)" xr:uid="{AAE3DAC9-2F67-419C-9124-8D39FC7D12A0}"/>
-    <hyperlink ref="C43" r:id="rId12" tooltip="约兰 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E8%98%AD_(%E7%8C%B6%E5%A4%A7)" xr:uid="{3E407794-BBC8-4C6C-8F8A-BF286D1FFEB8}"/>
-    <hyperlink ref="C42" r:id="rId13" tooltip="约沙法" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E6%B2%99%E6%B3%95" xr:uid="{860B15CA-7648-4BBC-9A4F-94015E44B37C}"/>
-    <hyperlink ref="C41" r:id="rId14" tooltip="亚撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E6%92%92" xr:uid="{7EE6A358-2023-427F-B2A7-D03CD2D3BCA4}"/>
-    <hyperlink ref="C40" r:id="rId15" tooltip="亚比央" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E6%AF%94%E5%A4%AE" xr:uid="{55B7F6CE-9AD5-4329-A895-769AC1D09E57}"/>
-    <hyperlink ref="C39" r:id="rId16" tooltip="罗波安" display="https://zh.wikipedia.org/wiki/%E7%BE%85%E6%B3%A2%E5%AE%89" xr:uid="{3EC3F7AA-B927-4AF4-A43C-876E512395BE}"/>
-    <hyperlink ref="C38" r:id="rId17" tooltip="所罗门 (君王)" display="https://zh.wikipedia.org/wiki/%E6%89%80%E7%BE%85%E9%96%80_(%E5%90%9B%E7%8E%8B)" xr:uid="{03B51CEB-C5A0-4737-BD85-A80A5286B1D3}"/>
-    <hyperlink ref="C37" r:id="rId18" tooltip="大卫王" display="https://zh.wikipedia.org/wiki/%E5%A4%A7%E8%A1%9B%E7%8E%8B" xr:uid="{80E557AD-A19A-47D5-A69C-8530541A76A5}"/>
-    <hyperlink ref="C57" r:id="rId19" xr:uid="{19DA0B9C-C79B-4D73-BD61-2298F262C554}"/>
+    <hyperlink ref="C53" r:id="rId1" tooltip="约雅敬" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E9%9B%85%E6%95%AC" xr:uid="{439A29C8-3C48-4332-A148-A1FE722B0B58}"/>
+    <hyperlink ref="C52" r:id="rId2" tooltip="约西亚" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E8%A5%BF%E4%BA%9E" xr:uid="{ECD3B9E9-B98F-4547-9106-7559A825DAD2}"/>
+    <hyperlink ref="C51" r:id="rId3" tooltip="亚们" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%80%91" xr:uid="{8732A9A7-D22A-495B-AC2C-00D8B92F93D9}"/>
+    <hyperlink ref="C50" r:id="rId4" tooltip="玛拿西 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%91%AA%E6%8B%BF%E8%A5%BF_(%E7%8C%B6%E5%A4%A7)" xr:uid="{3E6DBFCD-8A02-4D0A-97C9-9995E8C33208}"/>
+    <hyperlink ref="C49" r:id="rId5" tooltip="希西家" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E8%A5%BF%E5%AE%B6" xr:uid="{928A15B1-E352-48C2-B27F-F11E91FA7EA6}"/>
+    <hyperlink ref="C48" r:id="rId6" tooltip="亚哈斯" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%93%88%E6%96%AF" xr:uid="{0DC09F59-2904-4FBD-A9B8-FFDD9499A09E}"/>
+    <hyperlink ref="C47" r:id="rId7" tooltip="约坦" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E5%9D%A6" xr:uid="{6DE869B8-8245-4894-A5E3-E7B745007249}"/>
+    <hyperlink ref="C46" r:id="rId8" tooltip="乌西雅" xr:uid="{79334C27-6158-4B0E-B22D-93C5F10D9F42}"/>
+    <hyperlink ref="C45" r:id="rId9" tooltip="亚玛谢" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E7%91%AA%E8%AC%9D" xr:uid="{4E70B4E6-A86A-4406-B435-9CD8D5E6A131}"/>
+    <hyperlink ref="C44" r:id="rId10" tooltip="约阿施 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E9%98%BF%E6%96%BD_(%E7%8C%B6%E5%A4%A7)" xr:uid="{C59FD51A-5399-4F71-AA04-5C8794B167E1}"/>
+    <hyperlink ref="C43" r:id="rId11" tooltip="亚哈谢 (犹大)" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E5%93%88%E8%AC%9D_(%E7%8C%B6%E5%A4%A7)" xr:uid="{AAE3DAC9-2F67-419C-9124-8D39FC7D12A0}"/>
+    <hyperlink ref="C42" r:id="rId12" tooltip="约兰 (犹大)" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E8%98%AD_(%E7%8C%B6%E5%A4%A7)" xr:uid="{3E407794-BBC8-4C6C-8F8A-BF286D1FFEB8}"/>
+    <hyperlink ref="C41" r:id="rId13" tooltip="约沙法" display="https://zh.wikipedia.org/wiki/%E7%B4%84%E6%B2%99%E6%B3%95" xr:uid="{860B15CA-7648-4BBC-9A4F-94015E44B37C}"/>
+    <hyperlink ref="C40" r:id="rId14" tooltip="亚撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E6%92%92" xr:uid="{7EE6A358-2023-427F-B2A7-D03CD2D3BCA4}"/>
+    <hyperlink ref="C39" r:id="rId15" tooltip="亚比央" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E6%AF%94%E5%A4%AE" xr:uid="{55B7F6CE-9AD5-4329-A895-769AC1D09E57}"/>
+    <hyperlink ref="C38" r:id="rId16" tooltip="罗波安" display="https://zh.wikipedia.org/wiki/%E7%BE%85%E6%B3%A2%E5%AE%89" xr:uid="{3EC3F7AA-B927-4AF4-A43C-876E512395BE}"/>
+    <hyperlink ref="C37" r:id="rId17" tooltip="所罗门 (君王)" display="https://zh.wikipedia.org/wiki/%E6%89%80%E7%BE%85%E9%96%80_(%E5%90%9B%E7%8E%8B)" xr:uid="{03B51CEB-C5A0-4737-BD85-A80A5286B1D3}"/>
+    <hyperlink ref="C36" r:id="rId18" tooltip="大卫王" display="https://zh.wikipedia.org/wiki/%E5%A4%A7%E8%A1%9B%E7%8E%8B" xr:uid="{80E557AD-A19A-47D5-A69C-8530541A76A5}"/>
+    <hyperlink ref="C56" r:id="rId19" xr:uid="{19DA0B9C-C79B-4D73-BD61-2298F262C554}"/>
     <hyperlink ref="C4" r:id="rId20" tooltip="亚当" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E7%95%B6" xr:uid="{D91F2ECA-8206-403D-BF1E-7A61A39AFC4C}"/>
     <hyperlink ref="C5" r:id="rId21" tooltip="塞特" display="https://zh.wikipedia.org/wiki/%E5%A1%9E%E7%89%B9" xr:uid="{5682E5C8-9E0E-40CB-A11C-3E04AC1932F3}"/>
     <hyperlink ref="C6" r:id="rId22" tooltip="以挪士" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%8C%AA%E5%A3%AB" xr:uid="{3D22BE58-C482-4F3D-A9FD-4C4F20470042}"/>
@@ -3495,33 +3526,33 @@
     <hyperlink ref="C13" r:id="rId29" tooltip="挪亚" display="https://zh.wikipedia.org/wiki/%E6%8C%AA%E4%BA%9E" xr:uid="{9A10F4C0-14D5-4273-B40E-04B4BB16C1ED}"/>
     <hyperlink ref="C14" r:id="rId30" tooltip="闪 (圣经)" display="https://zh.wikipedia.org/wiki/%E9%96%83_(%E8%81%96%E7%B6%93)" xr:uid="{B5F37A7D-8280-4A5E-B393-85A2E0CBFA89}"/>
     <hyperlink ref="C15" r:id="rId31" tooltip="亚法撒" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E6%B3%95%E6%92%92" xr:uid="{9487E042-5D95-4BD1-8265-C1F67B23BB26}"/>
-    <hyperlink ref="C17" r:id="rId32" tooltip="沙拉 (圣经人物)" display="https://zh.wikipedia.org/wiki/%E6%B2%99%E6%8B%89_(%E5%9C%A3%E7%BB%8F%E4%BA%BA%E7%89%A9)" xr:uid="{70420CCF-87F7-4476-8446-2FBE69CFFB70}"/>
-    <hyperlink ref="C18" r:id="rId33" tooltip="希伯" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E4%BC%AF" xr:uid="{D6E27536-AE40-4A01-B2C0-EECAE77AA236}"/>
-    <hyperlink ref="C19" r:id="rId34" tooltip="法勒" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92" xr:uid="{9E7DE66B-3310-4766-8CF2-8A4700F92548}"/>
-    <hyperlink ref="C20" r:id="rId35" tooltip="拉吴" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E5%90%B4" xr:uid="{C4BC748A-4E43-4D88-8F45-3FF656DEDB70}"/>
-    <hyperlink ref="C21" r:id="rId36" tooltip="西鹿" display="https://zh.wikipedia.org/wiki/%E8%A5%BF%E9%B9%BF" xr:uid="{CD8C3835-2AC2-4D27-85DB-966FD3099464}"/>
-    <hyperlink ref="C22" r:id="rId37" tooltip="拿鹤" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%B9%A4" xr:uid="{63896651-57FE-4A10-A6FC-8877CFE2164B}"/>
-    <hyperlink ref="C23" r:id="rId38" tooltip="他拉" display="https://zh.wikipedia.org/wiki/%E4%BB%96%E6%8B%89" xr:uid="{D6088842-3C2D-401D-BA00-C30393CE0B21}"/>
-    <hyperlink ref="C24" r:id="rId39" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{4B892FC3-E34E-4ABF-BF9B-0986AA274D46}"/>
-    <hyperlink ref="C25" r:id="rId40" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{A9307EC9-C8C9-47ED-8219-7E3502B90F63}"/>
-    <hyperlink ref="C26" r:id="rId41" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{6A338BA4-EF55-4C71-AF27-7A5FBA074037}"/>
-    <hyperlink ref="C27" r:id="rId42" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{C6E79DDC-2A91-4A93-A384-2103381567D2}"/>
-    <hyperlink ref="C28" r:id="rId43" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{626B9A97-7547-420D-8C2A-1171F9746C8A}"/>
-    <hyperlink ref="C29" r:id="rId44" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{6FF395F4-4DD7-44FA-8809-496908535532}"/>
-    <hyperlink ref="C30" r:id="rId45" tooltip="亚兰" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E5%85%B0" xr:uid="{BFC871F3-C41F-4237-A422-066E1C6E8752}"/>
-    <hyperlink ref="C31" r:id="rId46" tooltip="亚米拿达" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E7%B1%B3%E6%8B%BF%E8%BE%BE" xr:uid="{DC54AF48-ABFF-436D-A79E-629582C19C8C}"/>
-    <hyperlink ref="C32" r:id="rId47" tooltip="拿顺" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%A1%BA" xr:uid="{6405FB9D-B96F-42ED-B1E0-5C7853932202}"/>
-    <hyperlink ref="C33" r:id="rId48" tooltip="撒门" display="https://zh.wikipedia.org/wiki/%E6%92%92%E9%97%A8" xr:uid="{C0E9A834-9566-4216-819F-14B61E7295BB}"/>
-    <hyperlink ref="C34" r:id="rId49" tooltip="波阿斯" display="https://zh.wikipedia.org/wiki/%E6%B3%A2%E9%98%BF%E6%96%AF" xr:uid="{91DB3C24-C842-44D0-B7A0-2B2FDC9AB3C1}"/>
-    <hyperlink ref="C35" r:id="rId50" tooltip="俄备得" display="https://zh.wikipedia.org/wiki/%E4%BF%84%E5%A4%87%E5%BE%97" xr:uid="{8234E72B-B474-4A3E-8B85-C04621638E2A}"/>
-    <hyperlink ref="C36" r:id="rId51" tooltip="耶西" display="https://zh.wikipedia.org/wiki/%E8%80%B6%E8%A5%BF" xr:uid="{11C68BAE-BF57-4E50-8EA2-F58C7EF02CC3}"/>
-    <hyperlink ref="C55" r:id="rId52" xr:uid="{1CC4AE70-C96A-4663-991A-C6C3C061D194}"/>
-    <hyperlink ref="D44" r:id="rId53" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{A357BE76-24D8-471A-B7BA-68629EFBACE2}"/>
-    <hyperlink ref="D45" r:id="rId54" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{47696524-5AD8-4A07-B660-AF10253EBFFF}"/>
-    <hyperlink ref="D46" r:id="rId55" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{971C962A-47BF-4EFF-AD02-EDEB2659F862}"/>
-    <hyperlink ref="D54" r:id="rId56" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约西亚生耶哥尼雅" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{79E51E53-FF4B-4187-8EE9-8A103052F237}"/>
-    <hyperlink ref="D56" r:id="rId57" location="%E7%AC%AC%E4%B8%89%E7%AB%A0" tooltip="耶哥尼雅被掳．他的儿子是撒拉铁、毘大雅......毘大雅的儿子是所罗巴伯......" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E5%8E%86%E4%BB%A3%E5%BF%97%E4%B8%8A - %E7%AC%AC%E4%B8%89%E7%AB%A0" xr:uid="{47116252-6F27-41AD-B956-8479A01C4E8D}"/>
-    <hyperlink ref="C67" r:id="rId58" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{1ECBF5AF-1065-423E-9ADD-3EE804376680}"/>
+    <hyperlink ref="C16" r:id="rId32" tooltip="沙拉 (圣经人物)" display="https://zh.wikipedia.org/wiki/%E6%B2%99%E6%8B%89_(%E5%9C%A3%E7%BB%8F%E4%BA%BA%E7%89%A9)" xr:uid="{70420CCF-87F7-4476-8446-2FBE69CFFB70}"/>
+    <hyperlink ref="C17" r:id="rId33" tooltip="希伯" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E4%BC%AF" xr:uid="{D6E27536-AE40-4A01-B2C0-EECAE77AA236}"/>
+    <hyperlink ref="C18" r:id="rId34" tooltip="法勒" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92" xr:uid="{9E7DE66B-3310-4766-8CF2-8A4700F92548}"/>
+    <hyperlink ref="C19" r:id="rId35" tooltip="拉吴" display="https://zh.wikipedia.org/wiki/%E6%8B%89%E5%90%B4" xr:uid="{C4BC748A-4E43-4D88-8F45-3FF656DEDB70}"/>
+    <hyperlink ref="C20" r:id="rId36" tooltip="西鹿" display="https://zh.wikipedia.org/wiki/%E8%A5%BF%E9%B9%BF" xr:uid="{CD8C3835-2AC2-4D27-85DB-966FD3099464}"/>
+    <hyperlink ref="C21" r:id="rId37" tooltip="拿鹤" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%B9%A4" xr:uid="{63896651-57FE-4A10-A6FC-8877CFE2164B}"/>
+    <hyperlink ref="C22" r:id="rId38" tooltip="他拉" display="https://zh.wikipedia.org/wiki/%E4%BB%96%E6%8B%89" xr:uid="{D6088842-3C2D-401D-BA00-C30393CE0B21}"/>
+    <hyperlink ref="C23" r:id="rId39" tooltip="亚伯拉罕" display="https://zh.wikipedia.org/wiki/%E4%BA%9E%E4%BC%AF%E6%8B%89%E7%BD%95" xr:uid="{4B892FC3-E34E-4ABF-BF9B-0986AA274D46}"/>
+    <hyperlink ref="C24" r:id="rId40" tooltip="以撒" display="https://zh.wikipedia.org/wiki/%E4%BB%A5%E6%92%92" xr:uid="{A9307EC9-C8C9-47ED-8219-7E3502B90F63}"/>
+    <hyperlink ref="C25" r:id="rId41" tooltip="雅各 (旧约圣经)" display="https://zh.wikipedia.org/wiki/%E9%9B%85%E5%90%84_(%E8%88%8A%E7%B4%84%E8%81%96%E7%B6%93)" xr:uid="{6A338BA4-EF55-4C71-AF27-7A5FBA074037}"/>
+    <hyperlink ref="C26" r:id="rId42" tooltip="犹大 (创世记)" display="https://zh.wikipedia.org/wiki/%E7%8C%B6%E5%A4%A7_(%E5%89%B5%E4%B8%96%E8%A8%98)" xr:uid="{C6E79DDC-2A91-4A93-A384-2103381567D2}"/>
+    <hyperlink ref="C27" r:id="rId43" tooltip="法勒斯" display="https://zh.wikipedia.org/wiki/%E6%B3%95%E5%8B%92%E6%96%AF" xr:uid="{626B9A97-7547-420D-8C2A-1171F9746C8A}"/>
+    <hyperlink ref="C28" r:id="rId44" tooltip="希斯仑" display="https://zh.wikipedia.org/wiki/%E5%B8%8C%E6%96%AF%E4%BB%91" xr:uid="{6FF395F4-4DD7-44FA-8809-496908535532}"/>
+    <hyperlink ref="C29" r:id="rId45" tooltip="亚兰" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E5%85%B0" xr:uid="{BFC871F3-C41F-4237-A422-066E1C6E8752}"/>
+    <hyperlink ref="C30" r:id="rId46" tooltip="亚米拿达" display="https://zh.wikipedia.org/wiki/%E4%BA%9A%E7%B1%B3%E6%8B%BF%E8%BE%BE" xr:uid="{DC54AF48-ABFF-436D-A79E-629582C19C8C}"/>
+    <hyperlink ref="C31" r:id="rId47" tooltip="拿顺" display="https://zh.wikipedia.org/wiki/%E6%8B%BF%E9%A1%BA" xr:uid="{6405FB9D-B96F-42ED-B1E0-5C7853932202}"/>
+    <hyperlink ref="C32" r:id="rId48" tooltip="撒门" display="https://zh.wikipedia.org/wiki/%E6%92%92%E9%97%A8" xr:uid="{C0E9A834-9566-4216-819F-14B61E7295BB}"/>
+    <hyperlink ref="C33" r:id="rId49" tooltip="波阿斯" display="https://zh.wikipedia.org/wiki/%E6%B3%A2%E9%98%BF%E6%96%AF" xr:uid="{91DB3C24-C842-44D0-B7A0-2B2FDC9AB3C1}"/>
+    <hyperlink ref="C34" r:id="rId50" tooltip="俄备得" display="https://zh.wikipedia.org/wiki/%E4%BF%84%E5%A4%87%E5%BE%97" xr:uid="{8234E72B-B474-4A3E-8B85-C04621638E2A}"/>
+    <hyperlink ref="C35" r:id="rId51" tooltip="耶西" display="https://zh.wikipedia.org/wiki/%E8%80%B6%E8%A5%BF" xr:uid="{11C68BAE-BF57-4E50-8EA2-F58C7EF02CC3}"/>
+    <hyperlink ref="C54" r:id="rId52" xr:uid="{1CC4AE70-C96A-4663-991A-C6C3C061D194}"/>
+    <hyperlink ref="D43" r:id="rId53" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{A357BE76-24D8-471A-B7BA-68629EFBACE2}"/>
+    <hyperlink ref="D44" r:id="rId54" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{47696524-5AD8-4A07-B660-AF10253EBFFF}"/>
+    <hyperlink ref="D45" r:id="rId55" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约兰生乌西亚" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{971C962A-47BF-4EFF-AD02-EDEB2659F862}"/>
+    <hyperlink ref="D53" r:id="rId56" location="%E7%AC%AC%E4%B8%80%E7%AB%A0" tooltip="约西亚生耶哥尼雅" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E9%A9%AC%E5%A4%AA%E7%A6%8F%E9%9F%B3 - %E7%AC%AC%E4%B8%80%E7%AB%A0" xr:uid="{79E51E53-FF4B-4187-8EE9-8A103052F237}"/>
+    <hyperlink ref="D55" r:id="rId57" location="%E7%AC%AC%E4%B8%89%E7%AB%A0" tooltip="耶哥尼雅被掳．他的儿子是撒拉铁、毘大雅......毘大雅的儿子是所罗巴伯......" display="https://zh.wikisource.org/wiki/%E5%9C%A3%E7%BB%8F_(%E5%92%8C%E5%90%88%E6%9C%AC)/%E5%8E%86%E4%BB%A3%E5%BF%97%E4%B8%8A - %E7%AC%AC%E4%B8%89%E7%AB%A0" xr:uid="{47116252-6F27-41AD-B956-8479A01C4E8D}"/>
+    <hyperlink ref="C66" r:id="rId58" display="https://zh.wikipedia.org/wiki/%E5%9C%A3%E8%8B%A5%E7%91%9F" xr:uid="{1ECBF5AF-1065-423E-9ADD-3EE804376680}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId59"/>
@@ -3529,10 +3560,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <pixelatorList sheetStid="1"/>
+  <pixelatorList sheetStid="2"/>
+</pixelators>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <woProps xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <woSheetsProps>
     <woSheetProps sheetStid="1" interlineOnOff="0" interlineColor="0" isDbSheet="0" isDashBoardSheet="0"/>
@@ -3543,20 +3581,22 @@
 </woProps>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
   <rangeList sheetStid="1" master=""/>
 </allowEditUser>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<pixelators xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <pixelatorList sheetStid="1"/>
-  <pixelatorList sheetStid="2"/>
-</pixelators>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06A0048C-2381-489B-AA07-9611017176EA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
@@ -3565,7 +3605,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06C82605-B75B-4693-9329-32AAD527C692}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
@@ -3574,20 +3614,11 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A5607D9-04D2-4DE1-AC0E-A7772F01BC71}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{224D003E-15C9-4FFE-AB16-9E66474EAE4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="https://web.wps.cn/et/2018/main"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>